--- a/data/vcp.xlsx
+++ b/data/vcp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6545ea455a795f0/Documentos/factsheets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{4BB71E4C-02F0-4AEF-B6C2-FF75E2C6216B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C17CC26-4CDE-405C-829C-DA6DA4F83E0D}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{4BB71E4C-02F0-4AEF-B6C2-FF75E2C6216B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52741CA-F316-4A6A-A7FD-6ACB47EAAE9C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B52BD4C8-FFA6-46E7-8C7A-5DBA6AEC6191}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>fecha</t>
   </si>
@@ -52,6 +52,18 @@
   <si>
     <t>gainvest_balanceado_pn</t>
   </si>
+  <si>
+    <t>gainvest_pesos_pn</t>
+  </si>
+  <si>
+    <t>gainvest_pesos_a</t>
+  </si>
+  <si>
+    <t>gainvest_pesos_b</t>
+  </si>
+  <si>
+    <t>gainvest_pesos_c</t>
+  </si>
 </sst>
 </file>
 
@@ -60,7 +72,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +86,15 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,19 +114,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{A311FBF1-5BEB-4C3E-8CC2-51E47AE4C94C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -437,13 +463,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83265F92-446E-4F95-B8F6-E30306C66F52}">
-  <dimension ref="A1:PQ414"/>
+  <dimension ref="A1:PP415"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:433" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,418 +487,18 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
-      <c r="AT1" s="1"/>
-      <c r="AU1" s="1"/>
-      <c r="AV1" s="1"/>
-      <c r="AW1" s="1"/>
-      <c r="AX1" s="1"/>
-      <c r="AY1" s="1"/>
-      <c r="AZ1" s="1"/>
-      <c r="BA1" s="1"/>
-      <c r="BB1" s="1"/>
-      <c r="BC1" s="1"/>
-      <c r="BD1" s="1"/>
-      <c r="BE1" s="1"/>
-      <c r="BF1" s="1"/>
-      <c r="BG1" s="1"/>
-      <c r="BH1" s="1"/>
-      <c r="BI1" s="1"/>
-      <c r="BJ1" s="1"/>
-      <c r="BK1" s="1"/>
-      <c r="BL1" s="1"/>
-      <c r="BM1" s="1"/>
-      <c r="BN1" s="1"/>
-      <c r="BO1" s="1"/>
-      <c r="BP1" s="1"/>
-      <c r="BQ1" s="1"/>
-      <c r="BR1" s="1"/>
-      <c r="BS1" s="1"/>
-      <c r="BT1" s="1"/>
-      <c r="BU1" s="1"/>
-      <c r="BV1" s="1"/>
-      <c r="BW1" s="1"/>
-      <c r="BX1" s="1"/>
-      <c r="BY1" s="1"/>
-      <c r="BZ1" s="1"/>
-      <c r="CA1" s="1"/>
-      <c r="CB1" s="1"/>
-      <c r="CC1" s="1"/>
-      <c r="CD1" s="1"/>
-      <c r="CE1" s="1"/>
-      <c r="CF1" s="1"/>
-      <c r="CG1" s="1"/>
-      <c r="CH1" s="1"/>
-      <c r="CI1" s="1"/>
-      <c r="CJ1" s="1"/>
-      <c r="CK1" s="1"/>
-      <c r="CL1" s="1"/>
-      <c r="CM1" s="1"/>
-      <c r="CN1" s="1"/>
-      <c r="CO1" s="1"/>
-      <c r="CP1" s="1"/>
-      <c r="CQ1" s="1"/>
-      <c r="CR1" s="1"/>
-      <c r="CS1" s="1"/>
-      <c r="CT1" s="1"/>
-      <c r="CU1" s="1"/>
-      <c r="CV1" s="1"/>
-      <c r="CW1" s="1"/>
-      <c r="CX1" s="1"/>
-      <c r="CY1" s="1"/>
-      <c r="CZ1" s="1"/>
-      <c r="DA1" s="1"/>
-      <c r="DB1" s="1"/>
-      <c r="DC1" s="1"/>
-      <c r="DD1" s="1"/>
-      <c r="DE1" s="1"/>
-      <c r="DF1" s="1"/>
-      <c r="DG1" s="1"/>
-      <c r="DH1" s="1"/>
-      <c r="DI1" s="1"/>
-      <c r="DJ1" s="1"/>
-      <c r="DK1" s="1"/>
-      <c r="DL1" s="1"/>
-      <c r="DM1" s="1"/>
-      <c r="DN1" s="1"/>
-      <c r="DO1" s="1"/>
-      <c r="DP1" s="1"/>
-      <c r="DQ1" s="1"/>
-      <c r="DR1" s="1"/>
-      <c r="DS1" s="1"/>
-      <c r="DT1" s="1"/>
-      <c r="DU1" s="1"/>
-      <c r="DV1" s="1"/>
-      <c r="DW1" s="1"/>
-      <c r="DX1" s="1"/>
-      <c r="DY1" s="1"/>
-      <c r="DZ1" s="1"/>
-      <c r="EA1" s="1"/>
-      <c r="EB1" s="1"/>
-      <c r="EC1" s="1"/>
-      <c r="ED1" s="1"/>
-      <c r="EE1" s="1"/>
-      <c r="EF1" s="1"/>
-      <c r="EG1" s="1"/>
-      <c r="EH1" s="1"/>
-      <c r="EI1" s="1"/>
-      <c r="EJ1" s="1"/>
-      <c r="EK1" s="1"/>
-      <c r="EL1" s="1"/>
-      <c r="EM1" s="1"/>
-      <c r="EN1" s="1"/>
-      <c r="EO1" s="1"/>
-      <c r="EP1" s="1"/>
-      <c r="EQ1" s="1"/>
-      <c r="ER1" s="1"/>
-      <c r="ES1" s="1"/>
-      <c r="ET1" s="1"/>
-      <c r="EU1" s="1"/>
-      <c r="EV1" s="1"/>
-      <c r="EW1" s="1"/>
-      <c r="EX1" s="1"/>
-      <c r="EY1" s="1"/>
-      <c r="EZ1" s="1"/>
-      <c r="FA1" s="1"/>
-      <c r="FB1" s="1"/>
-      <c r="FC1" s="1"/>
-      <c r="FD1" s="1"/>
-      <c r="FE1" s="1"/>
-      <c r="FF1" s="1"/>
-      <c r="FG1" s="1"/>
-      <c r="FH1" s="1"/>
-      <c r="FI1" s="1"/>
-      <c r="FJ1" s="1"/>
-      <c r="FK1" s="1"/>
-      <c r="FL1" s="1"/>
-      <c r="FM1" s="1"/>
-      <c r="FN1" s="1"/>
-      <c r="FO1" s="1"/>
-      <c r="FP1" s="1"/>
-      <c r="FQ1" s="1"/>
-      <c r="FR1" s="1"/>
-      <c r="FS1" s="1"/>
-      <c r="FT1" s="1"/>
-      <c r="FU1" s="1"/>
-      <c r="FV1" s="1"/>
-      <c r="FW1" s="1"/>
-      <c r="FX1" s="1"/>
-      <c r="FY1" s="1"/>
-      <c r="FZ1" s="1"/>
-      <c r="GA1" s="1"/>
-      <c r="GB1" s="1"/>
-      <c r="GC1" s="1"/>
-      <c r="GD1" s="1"/>
-      <c r="GE1" s="1"/>
-      <c r="GF1" s="1"/>
-      <c r="GG1" s="1"/>
-      <c r="GH1" s="1"/>
-      <c r="GI1" s="1"/>
-      <c r="GJ1" s="1"/>
-      <c r="GK1" s="1"/>
-      <c r="GL1" s="1"/>
-      <c r="GM1" s="1"/>
-      <c r="GN1" s="1"/>
-      <c r="GO1" s="1"/>
-      <c r="GP1" s="1"/>
-      <c r="GQ1" s="1"/>
-      <c r="GR1" s="1"/>
-      <c r="GS1" s="1"/>
-      <c r="GT1" s="1"/>
-      <c r="GU1" s="1"/>
-      <c r="GV1" s="1"/>
-      <c r="GW1" s="1"/>
-      <c r="GX1" s="1"/>
-      <c r="GY1" s="1"/>
-      <c r="GZ1" s="1"/>
-      <c r="HA1" s="1"/>
-      <c r="HB1" s="1"/>
-      <c r="HC1" s="1"/>
-      <c r="HD1" s="1"/>
-      <c r="HE1" s="1"/>
-      <c r="HF1" s="1"/>
-      <c r="HG1" s="1"/>
-      <c r="HH1" s="1"/>
-      <c r="HI1" s="1"/>
-      <c r="HJ1" s="1"/>
-      <c r="HK1" s="1"/>
-      <c r="HL1" s="1"/>
-      <c r="HM1" s="1"/>
-      <c r="HN1" s="1"/>
-      <c r="HO1" s="1"/>
-      <c r="HP1" s="1"/>
-      <c r="HQ1" s="1"/>
-      <c r="HR1" s="1"/>
-      <c r="HS1" s="1"/>
-      <c r="HT1" s="1"/>
-      <c r="HU1" s="1"/>
-      <c r="HV1" s="1"/>
-      <c r="HW1" s="1"/>
-      <c r="HX1" s="1"/>
-      <c r="HY1" s="1"/>
-      <c r="HZ1" s="1"/>
-      <c r="IA1" s="1"/>
-      <c r="IB1" s="1"/>
-      <c r="IC1" s="1"/>
-      <c r="ID1" s="1"/>
-      <c r="IE1" s="1"/>
-      <c r="IF1" s="1"/>
-      <c r="IG1" s="1"/>
-      <c r="IH1" s="1"/>
-      <c r="II1" s="1"/>
-      <c r="IJ1" s="1"/>
-      <c r="IK1" s="1"/>
-      <c r="IL1" s="1"/>
-      <c r="IM1" s="1"/>
-      <c r="IN1" s="1"/>
-      <c r="IO1" s="1"/>
-      <c r="IP1" s="1"/>
-      <c r="IQ1" s="1"/>
-      <c r="IR1" s="1"/>
-      <c r="IS1" s="1"/>
-      <c r="IT1" s="1"/>
-      <c r="IU1" s="1"/>
-      <c r="IV1" s="1"/>
-      <c r="IW1" s="1"/>
-      <c r="IX1" s="1"/>
-      <c r="IY1" s="1"/>
-      <c r="IZ1" s="1"/>
-      <c r="JA1" s="1"/>
-      <c r="JB1" s="1"/>
-      <c r="JC1" s="1"/>
-      <c r="JD1" s="1"/>
-      <c r="JE1" s="1"/>
-      <c r="JF1" s="1"/>
-      <c r="JG1" s="1"/>
-      <c r="JH1" s="1"/>
-      <c r="JI1" s="1"/>
-      <c r="JJ1" s="1"/>
-      <c r="JK1" s="1"/>
-      <c r="JL1" s="1"/>
-      <c r="JM1" s="1"/>
-      <c r="JN1" s="1"/>
-      <c r="JO1" s="1"/>
-      <c r="JP1" s="1"/>
-      <c r="JQ1" s="1"/>
-      <c r="JR1" s="1"/>
-      <c r="JS1" s="1"/>
-      <c r="JT1" s="1"/>
-      <c r="JU1" s="1"/>
-      <c r="JV1" s="1"/>
-      <c r="JW1" s="1"/>
-      <c r="JX1" s="1"/>
-      <c r="JY1" s="1"/>
-      <c r="JZ1" s="1"/>
-      <c r="KA1" s="1"/>
-      <c r="KB1" s="1"/>
-      <c r="KC1" s="1"/>
-      <c r="KD1" s="1"/>
-      <c r="KE1" s="1"/>
-      <c r="KF1" s="1"/>
-      <c r="KG1" s="1"/>
-      <c r="KH1" s="1"/>
-      <c r="KI1" s="1"/>
-      <c r="KJ1" s="1"/>
-      <c r="KK1" s="1"/>
-      <c r="KL1" s="1"/>
-      <c r="KM1" s="1"/>
-      <c r="KN1" s="1"/>
-      <c r="KO1" s="1"/>
-      <c r="KP1" s="1"/>
-      <c r="KQ1" s="1"/>
-      <c r="KR1" s="1"/>
-      <c r="KS1" s="1"/>
-      <c r="KT1" s="1"/>
-      <c r="KU1" s="1"/>
-      <c r="KV1" s="1"/>
-      <c r="KW1" s="1"/>
-      <c r="KX1" s="1"/>
-      <c r="KY1" s="1"/>
-      <c r="KZ1" s="1"/>
-      <c r="LA1" s="1"/>
-      <c r="LB1" s="1"/>
-      <c r="LC1" s="1"/>
-      <c r="LD1" s="1"/>
-      <c r="LE1" s="1"/>
-      <c r="LF1" s="1"/>
-      <c r="LG1" s="1"/>
-      <c r="LH1" s="1"/>
-      <c r="LI1" s="1"/>
-      <c r="LJ1" s="1"/>
-      <c r="LK1" s="1"/>
-      <c r="LL1" s="1"/>
-      <c r="LM1" s="1"/>
-      <c r="LN1" s="1"/>
-      <c r="LO1" s="1"/>
-      <c r="LP1" s="1"/>
-      <c r="LQ1" s="1"/>
-      <c r="LR1" s="1"/>
-      <c r="LS1" s="1"/>
-      <c r="LT1" s="1"/>
-      <c r="LU1" s="1"/>
-      <c r="LV1" s="1"/>
-      <c r="LW1" s="1"/>
-      <c r="LX1" s="1"/>
-      <c r="LY1" s="1"/>
-      <c r="LZ1" s="1"/>
-      <c r="MA1" s="1"/>
-      <c r="MB1" s="1"/>
-      <c r="MC1" s="1"/>
-      <c r="MD1" s="1"/>
-      <c r="ME1" s="1"/>
-      <c r="MF1" s="1"/>
-      <c r="MG1" s="1"/>
-      <c r="MH1" s="1"/>
-      <c r="MI1" s="1"/>
-      <c r="MJ1" s="1"/>
-      <c r="MK1" s="1"/>
-      <c r="ML1" s="1"/>
-      <c r="MM1" s="1"/>
-      <c r="MN1" s="1"/>
-      <c r="MO1" s="1"/>
-      <c r="MP1" s="1"/>
-      <c r="MQ1" s="1"/>
-      <c r="MR1" s="1"/>
-      <c r="MS1" s="1"/>
-      <c r="MT1" s="1"/>
-      <c r="MU1" s="1"/>
-      <c r="MV1" s="1"/>
-      <c r="MW1" s="1"/>
-      <c r="MX1" s="1"/>
-      <c r="MY1" s="1"/>
-      <c r="MZ1" s="1"/>
-      <c r="NA1" s="1"/>
-      <c r="NB1" s="1"/>
-      <c r="NC1" s="1"/>
-      <c r="ND1" s="1"/>
-      <c r="NE1" s="1"/>
-      <c r="NF1" s="1"/>
-      <c r="NG1" s="1"/>
-      <c r="NH1" s="1"/>
-      <c r="NI1" s="1"/>
-      <c r="NJ1" s="1"/>
-      <c r="NK1" s="1"/>
-      <c r="NL1" s="1"/>
-      <c r="NM1" s="1"/>
-      <c r="NN1" s="1"/>
-      <c r="NO1" s="1"/>
-      <c r="NP1" s="1"/>
-      <c r="NQ1" s="1"/>
-      <c r="NR1" s="1"/>
-      <c r="NS1" s="1"/>
-      <c r="NT1" s="1"/>
-      <c r="NU1" s="1"/>
-      <c r="NV1" s="1"/>
-      <c r="NW1" s="1"/>
-      <c r="NX1" s="1"/>
-      <c r="NY1" s="1"/>
-      <c r="NZ1" s="1"/>
-      <c r="OA1" s="1"/>
-      <c r="OB1" s="1"/>
-      <c r="OC1" s="1"/>
-      <c r="OD1" s="1"/>
-      <c r="OE1" s="1"/>
-      <c r="OF1" s="1"/>
-      <c r="OG1" s="1"/>
-      <c r="OH1" s="1"/>
-      <c r="OI1" s="1"/>
-      <c r="OJ1" s="1"/>
-      <c r="OK1" s="1"/>
-      <c r="OL1" s="1"/>
-      <c r="OM1" s="1"/>
-      <c r="ON1" s="1"/>
-      <c r="OO1" s="1"/>
-      <c r="OP1" s="1"/>
-      <c r="OQ1" s="1"/>
-      <c r="OR1" s="1"/>
-      <c r="OS1" s="1"/>
-      <c r="OT1" s="1"/>
-      <c r="OU1" s="1"/>
-      <c r="OV1" s="1"/>
-      <c r="OW1" s="1"/>
-      <c r="OX1" s="1"/>
-      <c r="OY1" s="1"/>
-      <c r="OZ1" s="1"/>
-      <c r="PA1" s="1"/>
-      <c r="PB1" s="1"/>
-      <c r="PC1" s="1"/>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
       <c r="PD1" s="1"/>
       <c r="PE1" s="1"/>
       <c r="PF1" s="1"/>
@@ -884,9 +512,8 @@
       <c r="PN1" s="1"/>
       <c r="PO1" s="1"/>
       <c r="PP1" s="1"/>
-      <c r="PQ1" s="1"/>
-    </row>
-    <row r="2" spans="1:433" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45721</v>
       </c>
@@ -902,419 +529,428 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
-      <c r="AT2" s="2"/>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2"/>
-      <c r="AX2" s="2"/>
-      <c r="AY2" s="2"/>
-      <c r="AZ2" s="2"/>
-      <c r="BA2" s="2"/>
-      <c r="BB2" s="2"/>
-      <c r="BC2" s="2"/>
-      <c r="BD2" s="2"/>
-      <c r="BE2" s="2"/>
-      <c r="BF2" s="2"/>
-      <c r="BG2" s="2"/>
-      <c r="BH2" s="2"/>
-      <c r="BI2" s="2"/>
-      <c r="BJ2" s="2"/>
-      <c r="BK2" s="2"/>
-      <c r="BL2" s="2"/>
-      <c r="BM2" s="2"/>
-      <c r="BN2" s="2"/>
-      <c r="BO2" s="2"/>
-      <c r="BP2" s="2"/>
-      <c r="BQ2" s="2"/>
-      <c r="BR2" s="2"/>
-      <c r="BS2" s="2"/>
-      <c r="BT2" s="2"/>
-      <c r="BU2" s="2"/>
-      <c r="BV2" s="2"/>
-      <c r="BW2" s="2"/>
-      <c r="BX2" s="2"/>
-      <c r="BY2" s="2"/>
-      <c r="BZ2" s="2"/>
-      <c r="CA2" s="2"/>
-      <c r="CB2" s="2"/>
-      <c r="CC2" s="2"/>
-      <c r="CD2" s="2"/>
-      <c r="CE2" s="2"/>
-      <c r="CF2" s="2"/>
-      <c r="CG2" s="2"/>
-      <c r="CH2" s="2"/>
-      <c r="CI2" s="2"/>
-      <c r="CJ2" s="2"/>
-      <c r="CK2" s="2"/>
-      <c r="CL2" s="2"/>
-      <c r="CM2" s="2"/>
-      <c r="CN2" s="2"/>
-      <c r="CO2" s="2"/>
-      <c r="CP2" s="2"/>
-      <c r="CQ2" s="2"/>
-      <c r="CR2" s="2"/>
-      <c r="CS2" s="2"/>
-      <c r="CT2" s="2"/>
-      <c r="CU2" s="2"/>
-      <c r="CV2" s="2"/>
-      <c r="CW2" s="2"/>
-      <c r="CX2" s="2"/>
-      <c r="CY2" s="2"/>
-      <c r="CZ2" s="2"/>
-      <c r="DA2" s="2"/>
-      <c r="DB2" s="2"/>
-      <c r="DC2" s="2"/>
-      <c r="DD2" s="2"/>
-      <c r="DE2" s="2"/>
-      <c r="DF2" s="2"/>
-      <c r="DG2" s="2"/>
-      <c r="DH2" s="2"/>
-      <c r="DI2" s="2"/>
-      <c r="DJ2" s="2"/>
-      <c r="DK2" s="2"/>
-      <c r="DL2" s="2"/>
-      <c r="DM2" s="2"/>
-      <c r="DN2" s="2"/>
-      <c r="DO2" s="2"/>
-      <c r="DP2" s="2"/>
-      <c r="DQ2" s="2"/>
-      <c r="DR2" s="2"/>
-      <c r="DS2" s="2"/>
-      <c r="DT2" s="2"/>
-      <c r="DU2" s="2"/>
-      <c r="DV2" s="2"/>
-      <c r="DW2" s="2"/>
-      <c r="DX2" s="2"/>
-      <c r="DY2" s="2"/>
-      <c r="DZ2" s="2"/>
-      <c r="EA2" s="2"/>
-      <c r="EB2" s="2"/>
-      <c r="EC2" s="2"/>
-      <c r="ED2" s="2"/>
-      <c r="EE2" s="2"/>
-      <c r="EF2" s="2"/>
-      <c r="EG2" s="2"/>
-      <c r="EH2" s="2"/>
-      <c r="EI2" s="2"/>
-      <c r="EJ2" s="2"/>
-      <c r="EK2" s="2"/>
-      <c r="EL2" s="2"/>
-      <c r="EM2" s="2"/>
-      <c r="EN2" s="2"/>
-      <c r="EO2" s="2"/>
-      <c r="EP2" s="2"/>
-      <c r="EQ2" s="2"/>
-      <c r="ER2" s="2"/>
-      <c r="ES2" s="2"/>
-      <c r="ET2" s="2"/>
-      <c r="EU2" s="2"/>
-      <c r="EV2" s="2"/>
-      <c r="EW2" s="2"/>
-      <c r="EX2" s="2"/>
-      <c r="EY2" s="2"/>
-      <c r="EZ2" s="2"/>
-      <c r="FA2" s="2"/>
-      <c r="FB2" s="2"/>
-      <c r="FC2" s="2"/>
-      <c r="FD2" s="2"/>
-      <c r="FE2" s="2"/>
-      <c r="FF2" s="2"/>
-      <c r="FG2" s="2"/>
-      <c r="FH2" s="2"/>
-      <c r="FI2" s="2"/>
-      <c r="FJ2" s="2"/>
-      <c r="FK2" s="2"/>
-      <c r="FL2" s="2"/>
-      <c r="FM2" s="2"/>
-      <c r="FN2" s="2"/>
-      <c r="FO2" s="2"/>
-      <c r="FP2" s="2"/>
-      <c r="FQ2" s="2"/>
-      <c r="FR2" s="2"/>
-      <c r="FS2" s="2"/>
-      <c r="FT2" s="2"/>
-      <c r="FU2" s="2"/>
-      <c r="FV2" s="2"/>
-      <c r="FW2" s="2"/>
-      <c r="FX2" s="2"/>
-      <c r="FY2" s="2"/>
-      <c r="FZ2" s="2"/>
-      <c r="GA2" s="2"/>
-      <c r="GB2" s="2"/>
-      <c r="GC2" s="2"/>
-      <c r="GD2" s="2"/>
-      <c r="GE2" s="2"/>
-      <c r="GF2" s="2"/>
-      <c r="GG2" s="2"/>
-      <c r="GH2" s="2"/>
-      <c r="GI2" s="2"/>
-      <c r="GJ2" s="2"/>
-      <c r="GK2" s="2"/>
-      <c r="GL2" s="2"/>
-      <c r="GM2" s="2"/>
-      <c r="GN2" s="2"/>
-      <c r="GO2" s="2"/>
-      <c r="GP2" s="2"/>
-      <c r="GQ2" s="2"/>
-      <c r="GR2" s="2"/>
-      <c r="GS2" s="2"/>
-      <c r="GT2" s="2"/>
-      <c r="GU2" s="2"/>
-      <c r="GV2" s="2"/>
-      <c r="GW2" s="2"/>
-      <c r="GX2" s="2"/>
-      <c r="GY2" s="2"/>
-      <c r="GZ2" s="2"/>
-      <c r="HA2" s="2"/>
-      <c r="HB2" s="2"/>
-      <c r="HC2" s="2"/>
-      <c r="HD2" s="2"/>
-      <c r="HE2" s="2"/>
-      <c r="HF2" s="2"/>
-      <c r="HG2" s="2"/>
-      <c r="HH2" s="2"/>
-      <c r="HI2" s="2"/>
-      <c r="HJ2" s="2"/>
-      <c r="HK2" s="2"/>
-      <c r="HL2" s="2"/>
-      <c r="HM2" s="2"/>
-      <c r="HN2" s="2"/>
-      <c r="HO2" s="2"/>
-      <c r="HP2" s="2"/>
-      <c r="HQ2" s="2"/>
-      <c r="HR2" s="2"/>
-      <c r="HS2" s="2"/>
-      <c r="HT2" s="2"/>
-      <c r="HU2" s="2"/>
-      <c r="HV2" s="2"/>
-      <c r="HW2" s="2"/>
-      <c r="HX2" s="2"/>
-      <c r="HY2" s="2"/>
-      <c r="HZ2" s="2"/>
-      <c r="IA2" s="2"/>
-      <c r="IB2" s="2"/>
-      <c r="IC2" s="2"/>
-      <c r="ID2" s="2"/>
-      <c r="IE2" s="2"/>
-      <c r="IF2" s="2"/>
-      <c r="IG2" s="2"/>
-      <c r="IH2" s="2"/>
-      <c r="II2" s="2"/>
-      <c r="IJ2" s="2"/>
-      <c r="IK2" s="2"/>
-      <c r="IL2" s="2"/>
-      <c r="IM2" s="2"/>
-      <c r="IN2" s="2"/>
-      <c r="IO2" s="2"/>
-      <c r="IP2" s="2"/>
-      <c r="IQ2" s="2"/>
-      <c r="IR2" s="2"/>
-      <c r="IS2" s="2"/>
-      <c r="IT2" s="2"/>
-      <c r="IU2" s="2"/>
-      <c r="IV2" s="2"/>
-      <c r="IW2" s="2"/>
-      <c r="IX2" s="2"/>
-      <c r="IY2" s="2"/>
-      <c r="IZ2" s="2"/>
-      <c r="JA2" s="2"/>
-      <c r="JB2" s="2"/>
-      <c r="JC2" s="2"/>
-      <c r="JD2" s="2"/>
-      <c r="JE2" s="2"/>
-      <c r="JF2" s="2"/>
-      <c r="JG2" s="2"/>
-      <c r="JH2" s="2"/>
-      <c r="JI2" s="2"/>
-      <c r="JJ2" s="2"/>
-      <c r="JK2" s="2"/>
-      <c r="JL2" s="2"/>
-      <c r="JM2" s="2"/>
-      <c r="JN2" s="2"/>
-      <c r="JO2" s="2"/>
-      <c r="JP2" s="2"/>
-      <c r="JQ2" s="2"/>
-      <c r="JR2" s="2"/>
-      <c r="JS2" s="2"/>
-      <c r="JT2" s="2"/>
-      <c r="JU2" s="2"/>
-      <c r="JV2" s="2"/>
-      <c r="JW2" s="2"/>
-      <c r="JX2" s="2"/>
-      <c r="JY2" s="2"/>
-      <c r="JZ2" s="2"/>
-      <c r="KA2" s="2"/>
-      <c r="KB2" s="2"/>
-      <c r="KC2" s="2"/>
-      <c r="KD2" s="2"/>
-      <c r="KE2" s="2"/>
-      <c r="KF2" s="2"/>
-      <c r="KG2" s="2"/>
-      <c r="KH2" s="2"/>
-      <c r="KI2" s="2"/>
-      <c r="KJ2" s="2"/>
-      <c r="KK2" s="2"/>
-      <c r="KL2" s="2"/>
-      <c r="KM2" s="2"/>
-      <c r="KN2" s="2"/>
-      <c r="KO2" s="2"/>
-      <c r="KP2" s="2"/>
-      <c r="KQ2" s="2"/>
-      <c r="KR2" s="2"/>
-      <c r="KS2" s="2"/>
-      <c r="KT2" s="2"/>
-      <c r="KU2" s="2"/>
-      <c r="KV2" s="2"/>
-      <c r="KW2" s="2"/>
-      <c r="KX2" s="2"/>
-      <c r="KY2" s="2"/>
-      <c r="KZ2" s="2"/>
-      <c r="LA2" s="2"/>
-      <c r="LB2" s="2"/>
-      <c r="LC2" s="2"/>
-      <c r="LD2" s="2"/>
-      <c r="LE2" s="2"/>
-      <c r="LF2" s="2"/>
-      <c r="LG2" s="2"/>
-      <c r="LH2" s="2"/>
-      <c r="LI2" s="2"/>
-      <c r="LJ2" s="2"/>
-      <c r="LK2" s="2"/>
-      <c r="LL2" s="2"/>
-      <c r="LM2" s="2"/>
-      <c r="LN2" s="2"/>
-      <c r="LO2" s="2"/>
-      <c r="LP2" s="2"/>
-      <c r="LQ2" s="2"/>
-      <c r="LR2" s="2"/>
-      <c r="LS2" s="2"/>
-      <c r="LT2" s="2"/>
-      <c r="LU2" s="2"/>
-      <c r="LV2" s="2"/>
-      <c r="LW2" s="2"/>
-      <c r="LX2" s="2"/>
-      <c r="LY2" s="2"/>
-      <c r="LZ2" s="2"/>
-      <c r="MA2" s="2"/>
-      <c r="MB2" s="2"/>
-      <c r="MC2" s="2"/>
-      <c r="MD2" s="2"/>
-      <c r="ME2" s="2"/>
-      <c r="MF2" s="2"/>
-      <c r="MG2" s="2"/>
-      <c r="MH2" s="2"/>
-      <c r="MI2" s="2"/>
-      <c r="MJ2" s="2"/>
-      <c r="MK2" s="2"/>
-      <c r="ML2" s="2"/>
-      <c r="MM2" s="2"/>
-      <c r="MN2" s="2"/>
-      <c r="MO2" s="2"/>
-      <c r="MP2" s="2"/>
-      <c r="MQ2" s="2"/>
-      <c r="MR2" s="2"/>
-      <c r="MS2" s="2"/>
-      <c r="MT2" s="2"/>
-      <c r="MU2" s="2"/>
-      <c r="MV2" s="2"/>
-      <c r="MW2" s="2"/>
-      <c r="MX2" s="2"/>
-      <c r="MY2" s="2"/>
-      <c r="MZ2" s="2"/>
-      <c r="NA2" s="2"/>
-      <c r="NB2" s="2"/>
-      <c r="NC2" s="2"/>
-      <c r="ND2" s="2"/>
-      <c r="NE2" s="2"/>
-      <c r="NF2" s="2"/>
-      <c r="NG2" s="2"/>
-      <c r="NH2" s="2"/>
-      <c r="NI2" s="2"/>
-      <c r="NJ2" s="2"/>
-      <c r="NK2" s="2"/>
-      <c r="NL2" s="2"/>
-      <c r="NM2" s="2"/>
-      <c r="NN2" s="2"/>
-      <c r="NO2" s="2"/>
-      <c r="NP2" s="2"/>
-      <c r="NQ2" s="2"/>
-      <c r="NR2" s="2"/>
-      <c r="NS2" s="2"/>
-      <c r="NT2" s="2"/>
-      <c r="NU2" s="2"/>
-      <c r="NV2" s="2"/>
-      <c r="NW2" s="2"/>
-      <c r="NX2" s="2"/>
-      <c r="NY2" s="2"/>
-      <c r="NZ2" s="2"/>
-      <c r="OA2" s="2"/>
-      <c r="OB2" s="2"/>
-      <c r="OC2" s="2"/>
-      <c r="OD2" s="2"/>
-      <c r="OE2" s="2"/>
-      <c r="OF2" s="2"/>
-      <c r="OG2" s="2"/>
-      <c r="OH2" s="2"/>
-      <c r="OI2" s="2"/>
-      <c r="OJ2" s="2"/>
-      <c r="OK2" s="2"/>
-      <c r="OL2" s="2"/>
-      <c r="OM2" s="2"/>
-      <c r="ON2" s="2"/>
-      <c r="OO2" s="2"/>
-      <c r="OP2" s="2"/>
-      <c r="OQ2" s="2"/>
-      <c r="OR2" s="2"/>
-      <c r="OS2" s="2"/>
-      <c r="OT2" s="2"/>
-      <c r="OU2" s="2"/>
-      <c r="OV2" s="2"/>
-      <c r="OW2" s="2"/>
-      <c r="OX2" s="2"/>
-      <c r="OY2" s="2"/>
-      <c r="OZ2" s="2"/>
-      <c r="PA2" s="2"/>
-      <c r="PB2" s="2"/>
-      <c r="PC2" s="2"/>
+      <c r="F2" s="3">
+        <v>94006043497.789993</v>
+      </c>
+      <c r="G2">
+        <v>3.9011900000000002</v>
+      </c>
+      <c r="H2">
+        <v>28.919828000000003</v>
+      </c>
+      <c r="I2">
+        <v>28.919063999999999</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="4"/>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
+      <c r="AP2" s="4"/>
+      <c r="AQ2" s="4"/>
+      <c r="AR2" s="4"/>
+      <c r="AS2" s="4"/>
+      <c r="AT2" s="4"/>
+      <c r="AU2" s="4"/>
+      <c r="AV2" s="4"/>
+      <c r="AW2" s="4"/>
+      <c r="AX2" s="4"/>
+      <c r="AY2" s="4"/>
+      <c r="AZ2" s="4"/>
+      <c r="BA2" s="4"/>
+      <c r="BB2" s="4"/>
+      <c r="BC2" s="4"/>
+      <c r="BD2" s="4"/>
+      <c r="BE2" s="4"/>
+      <c r="BF2" s="4"/>
+      <c r="BG2" s="4"/>
+      <c r="BH2" s="4"/>
+      <c r="BI2" s="4"/>
+      <c r="BJ2" s="4"/>
+      <c r="BK2" s="4"/>
+      <c r="BL2" s="4"/>
+      <c r="BM2" s="4"/>
+      <c r="BN2" s="4"/>
+      <c r="BO2" s="4"/>
+      <c r="BP2" s="4"/>
+      <c r="BQ2" s="4"/>
+      <c r="BR2" s="4"/>
+      <c r="BS2" s="4"/>
+      <c r="BT2" s="4"/>
+      <c r="BU2" s="4"/>
+      <c r="BV2" s="4"/>
+      <c r="BW2" s="4"/>
+      <c r="BX2" s="4"/>
+      <c r="BY2" s="4"/>
+      <c r="BZ2" s="4"/>
+      <c r="CA2" s="4"/>
+      <c r="CB2" s="4"/>
+      <c r="CC2" s="4"/>
+      <c r="CD2" s="4"/>
+      <c r="CE2" s="4"/>
+      <c r="CF2" s="4"/>
+      <c r="CG2" s="4"/>
+      <c r="CH2" s="4"/>
+      <c r="CI2" s="4"/>
+      <c r="CJ2" s="4"/>
+      <c r="CK2" s="4"/>
+      <c r="CL2" s="4"/>
+      <c r="CM2" s="4"/>
+      <c r="CN2" s="4"/>
+      <c r="CO2" s="4"/>
+      <c r="CP2" s="4"/>
+      <c r="CQ2" s="4"/>
+      <c r="CR2" s="4"/>
+      <c r="CS2" s="4"/>
+      <c r="CT2" s="4"/>
+      <c r="CU2" s="4"/>
+      <c r="CV2" s="4"/>
+      <c r="CW2" s="4"/>
+      <c r="CX2" s="4"/>
+      <c r="CY2" s="4"/>
+      <c r="CZ2" s="4"/>
+      <c r="DA2" s="4"/>
+      <c r="DB2" s="4"/>
+      <c r="DC2" s="4"/>
+      <c r="DD2" s="4"/>
+      <c r="DE2" s="4"/>
+      <c r="DF2" s="4"/>
+      <c r="DG2" s="4"/>
+      <c r="DH2" s="4"/>
+      <c r="DI2" s="4"/>
+      <c r="DJ2" s="4"/>
+      <c r="DK2" s="4"/>
+      <c r="DL2" s="4"/>
+      <c r="DM2" s="4"/>
+      <c r="DN2" s="4"/>
+      <c r="DO2" s="4"/>
+      <c r="DP2" s="4"/>
+      <c r="DQ2" s="4"/>
+      <c r="DR2" s="4"/>
+      <c r="DS2" s="4"/>
+      <c r="DT2" s="4"/>
+      <c r="DU2" s="4"/>
+      <c r="DV2" s="4"/>
+      <c r="DW2" s="4"/>
+      <c r="DX2" s="4"/>
+      <c r="DY2" s="4"/>
+      <c r="DZ2" s="4"/>
+      <c r="EA2" s="4"/>
+      <c r="EB2" s="4"/>
+      <c r="EC2" s="4"/>
+      <c r="ED2" s="4"/>
+      <c r="EE2" s="4"/>
+      <c r="EF2" s="4"/>
+      <c r="EG2" s="4"/>
+      <c r="EH2" s="4"/>
+      <c r="EI2" s="4"/>
+      <c r="EJ2" s="4"/>
+      <c r="EK2" s="4"/>
+      <c r="EL2" s="4"/>
+      <c r="EM2" s="4"/>
+      <c r="EN2" s="4"/>
+      <c r="EO2" s="4"/>
+      <c r="EP2" s="4"/>
+      <c r="EQ2" s="4"/>
+      <c r="ER2" s="4"/>
+      <c r="ES2" s="4"/>
+      <c r="ET2" s="4"/>
+      <c r="EU2" s="4"/>
+      <c r="EV2" s="4"/>
+      <c r="EW2" s="4"/>
+      <c r="EX2" s="4"/>
+      <c r="EY2" s="4"/>
+      <c r="EZ2" s="4"/>
+      <c r="FA2" s="4"/>
+      <c r="FB2" s="4"/>
+      <c r="FC2" s="4"/>
+      <c r="FD2" s="4"/>
+      <c r="FE2" s="4"/>
+      <c r="FF2" s="4"/>
+      <c r="FG2" s="4"/>
+      <c r="FH2" s="4"/>
+      <c r="FI2" s="4"/>
+      <c r="FJ2" s="4"/>
+      <c r="FK2" s="4"/>
+      <c r="FL2" s="4"/>
+      <c r="FM2" s="4"/>
+      <c r="FN2" s="4"/>
+      <c r="FO2" s="4"/>
+      <c r="FP2" s="4"/>
+      <c r="FQ2" s="4"/>
+      <c r="FR2" s="4"/>
+      <c r="FS2" s="4"/>
+      <c r="FT2" s="4"/>
+      <c r="FU2" s="4"/>
+      <c r="FV2" s="4"/>
+      <c r="FW2" s="4"/>
+      <c r="FX2" s="4"/>
+      <c r="FY2" s="4"/>
+      <c r="FZ2" s="4"/>
+      <c r="GA2" s="4"/>
+      <c r="GB2" s="4"/>
+      <c r="GC2" s="4"/>
+      <c r="GD2" s="4"/>
+      <c r="GE2" s="4"/>
+      <c r="GF2" s="4"/>
+      <c r="GG2" s="4"/>
+      <c r="GH2" s="4"/>
+      <c r="GI2" s="4"/>
+      <c r="GJ2" s="4"/>
+      <c r="GK2" s="4"/>
+      <c r="GL2" s="4"/>
+      <c r="GM2" s="4"/>
+      <c r="GN2" s="4"/>
+      <c r="GO2" s="4"/>
+      <c r="GP2" s="4"/>
+      <c r="GQ2" s="4"/>
+      <c r="GR2" s="4"/>
+      <c r="GS2" s="4"/>
+      <c r="GT2" s="4"/>
+      <c r="GU2" s="4"/>
+      <c r="GV2" s="4"/>
+      <c r="GW2" s="4"/>
+      <c r="GX2" s="4"/>
+      <c r="GY2" s="4"/>
+      <c r="GZ2" s="4"/>
+      <c r="HA2" s="4"/>
+      <c r="HB2" s="4"/>
+      <c r="HC2" s="4"/>
+      <c r="HD2" s="4"/>
+      <c r="HE2" s="4"/>
+      <c r="HF2" s="4"/>
+      <c r="HG2" s="4"/>
+      <c r="HH2" s="4"/>
+      <c r="HI2" s="4"/>
+      <c r="HJ2" s="4"/>
+      <c r="HK2" s="4"/>
+      <c r="HL2" s="4"/>
+      <c r="HM2" s="4"/>
+      <c r="HN2" s="4"/>
+      <c r="HO2" s="4"/>
+      <c r="HP2" s="4"/>
+      <c r="HQ2" s="4"/>
+      <c r="HR2" s="4"/>
+      <c r="HS2" s="4"/>
+      <c r="HT2" s="4"/>
+      <c r="HU2" s="4"/>
+      <c r="HV2" s="4"/>
+      <c r="HW2" s="4"/>
+      <c r="HX2" s="4"/>
+      <c r="HY2" s="4"/>
+      <c r="HZ2" s="4"/>
+      <c r="IA2" s="4"/>
+      <c r="IB2" s="4"/>
+      <c r="IC2" s="4"/>
+      <c r="ID2" s="4"/>
+      <c r="IE2" s="4"/>
+      <c r="IF2" s="4"/>
+      <c r="IG2" s="4"/>
+      <c r="IH2" s="4"/>
+      <c r="II2" s="4"/>
+      <c r="IJ2" s="4"/>
+      <c r="IK2" s="4"/>
+      <c r="IL2" s="4"/>
+      <c r="IM2" s="4"/>
+      <c r="IN2" s="4"/>
+      <c r="IO2" s="4"/>
+      <c r="IP2" s="4"/>
+      <c r="IQ2" s="4"/>
+      <c r="IR2" s="4"/>
+      <c r="IS2" s="4"/>
+      <c r="IT2" s="4"/>
+      <c r="IU2" s="4"/>
+      <c r="IV2" s="4"/>
+      <c r="IW2" s="4"/>
+      <c r="IX2" s="4"/>
+      <c r="IY2" s="4"/>
+      <c r="IZ2" s="4"/>
+      <c r="JA2" s="4"/>
+      <c r="JB2" s="4"/>
+      <c r="JC2" s="4"/>
+      <c r="JD2" s="4"/>
+      <c r="JE2" s="4"/>
+      <c r="JF2" s="4"/>
+      <c r="JG2" s="4"/>
+      <c r="JH2" s="4"/>
+      <c r="JI2" s="4"/>
+      <c r="JJ2" s="4"/>
+      <c r="JK2" s="4"/>
+      <c r="JL2" s="4"/>
+      <c r="JM2" s="4"/>
+      <c r="JN2" s="4"/>
+      <c r="JO2" s="4"/>
+      <c r="JP2" s="4"/>
+      <c r="JQ2" s="4"/>
+      <c r="JR2" s="4"/>
+      <c r="JS2" s="4"/>
+      <c r="JT2" s="4"/>
+      <c r="JU2" s="4"/>
+      <c r="JV2" s="4"/>
+      <c r="JW2" s="4"/>
+      <c r="JX2" s="4"/>
+      <c r="JY2" s="4"/>
+      <c r="JZ2" s="4"/>
+      <c r="KA2" s="4"/>
+      <c r="KB2" s="4"/>
+      <c r="KC2" s="4"/>
+      <c r="KD2" s="4"/>
+      <c r="KE2" s="4"/>
+      <c r="KF2" s="4"/>
+      <c r="KG2" s="4"/>
+      <c r="KH2" s="4"/>
+      <c r="KI2" s="4"/>
+      <c r="KJ2" s="4"/>
+      <c r="KK2" s="4"/>
+      <c r="KL2" s="4"/>
+      <c r="KM2" s="4"/>
+      <c r="KN2" s="4"/>
+      <c r="KO2" s="4"/>
+      <c r="KP2" s="4"/>
+      <c r="KQ2" s="4"/>
+      <c r="KR2" s="4"/>
+      <c r="KS2" s="4"/>
+      <c r="KT2" s="4"/>
+      <c r="KU2" s="4"/>
+      <c r="KV2" s="4"/>
+      <c r="KW2" s="4"/>
+      <c r="KX2" s="4"/>
+      <c r="KY2" s="4"/>
+      <c r="KZ2" s="4"/>
+      <c r="LA2" s="4"/>
+      <c r="LB2" s="4"/>
+      <c r="LC2" s="4"/>
+      <c r="LD2" s="4"/>
+      <c r="LE2" s="4"/>
+      <c r="LF2" s="4"/>
+      <c r="LG2" s="4"/>
+      <c r="LH2" s="4"/>
+      <c r="LI2" s="4"/>
+      <c r="LJ2" s="4"/>
+      <c r="LK2" s="4"/>
+      <c r="LL2" s="4"/>
+      <c r="LM2" s="4"/>
+      <c r="LN2" s="4"/>
+      <c r="LO2" s="4"/>
+      <c r="LP2" s="4"/>
+      <c r="LQ2" s="4"/>
+      <c r="LR2" s="4"/>
+      <c r="LS2" s="4"/>
+      <c r="LT2" s="4"/>
+      <c r="LU2" s="4"/>
+      <c r="LV2" s="4"/>
+      <c r="LW2" s="4"/>
+      <c r="LX2" s="4"/>
+      <c r="LY2" s="4"/>
+      <c r="LZ2" s="4"/>
+      <c r="MA2" s="4"/>
+      <c r="MB2" s="4"/>
+      <c r="MC2" s="4"/>
+      <c r="MD2" s="4"/>
+      <c r="ME2" s="4"/>
+      <c r="MF2" s="4"/>
+      <c r="MG2" s="4"/>
+      <c r="MH2" s="4"/>
+      <c r="MI2" s="4"/>
+      <c r="MJ2" s="4"/>
+      <c r="MK2" s="4"/>
+      <c r="ML2" s="4"/>
+      <c r="MM2" s="4"/>
+      <c r="MN2" s="4"/>
+      <c r="MO2" s="4"/>
+      <c r="MP2" s="4"/>
+      <c r="MQ2" s="4"/>
+      <c r="MR2" s="4"/>
+      <c r="MS2" s="4"/>
+      <c r="MT2" s="4"/>
+      <c r="MU2" s="4"/>
+      <c r="MV2" s="4"/>
+      <c r="MW2" s="4"/>
+      <c r="MX2" s="4"/>
+      <c r="MY2" s="4"/>
+      <c r="MZ2" s="4"/>
+      <c r="NA2" s="4"/>
+      <c r="NB2" s="4"/>
+      <c r="NC2" s="4"/>
+      <c r="ND2" s="4"/>
+      <c r="NE2" s="4"/>
+      <c r="NF2" s="4"/>
+      <c r="NG2" s="4"/>
+      <c r="NH2" s="4"/>
+      <c r="NI2" s="4"/>
+      <c r="NJ2" s="4"/>
+      <c r="NK2" s="4"/>
+      <c r="NL2" s="4"/>
+      <c r="NM2" s="4"/>
+      <c r="NN2" s="4"/>
+      <c r="NO2" s="4"/>
+      <c r="NP2" s="4"/>
+      <c r="NQ2" s="4"/>
+      <c r="NR2" s="4"/>
+      <c r="NS2" s="4"/>
+      <c r="NT2" s="4"/>
+      <c r="NU2" s="4"/>
+      <c r="NV2" s="4"/>
+      <c r="NW2" s="4"/>
+      <c r="NX2" s="4"/>
+      <c r="NY2" s="4"/>
+      <c r="NZ2" s="4"/>
+      <c r="OA2" s="4"/>
+      <c r="OB2" s="4"/>
+      <c r="OC2" s="4"/>
+      <c r="OD2" s="4"/>
+      <c r="OE2" s="4"/>
+      <c r="OF2" s="4"/>
+      <c r="OG2" s="4"/>
+      <c r="OH2" s="4"/>
+      <c r="OI2" s="4"/>
+      <c r="OJ2" s="4"/>
+      <c r="OK2" s="4"/>
+      <c r="OL2" s="4"/>
+      <c r="OM2" s="4"/>
+      <c r="ON2" s="4"/>
+      <c r="OO2" s="4"/>
+      <c r="OP2" s="4"/>
+      <c r="OQ2" s="4"/>
+      <c r="OR2" s="4"/>
+      <c r="OS2" s="4"/>
+      <c r="OT2" s="4"/>
+      <c r="OU2" s="4"/>
+      <c r="OV2" s="4"/>
+      <c r="OW2" s="4"/>
+      <c r="OX2" s="4"/>
+      <c r="OY2" s="4"/>
+      <c r="OZ2" s="4"/>
+      <c r="PA2" s="4"/>
+      <c r="PB2" s="4"/>
+      <c r="PC2" s="4"/>
       <c r="PD2" s="2"/>
       <c r="PE2" s="2"/>
       <c r="PF2" s="2"/>
@@ -1328,9 +964,8 @@
       <c r="PN2" s="2"/>
       <c r="PO2" s="2"/>
       <c r="PP2" s="2"/>
-      <c r="PQ2" s="2"/>
-    </row>
-    <row r="3" spans="1:433" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45722</v>
       </c>
@@ -1346,9 +981,18 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="F3" s="3">
+        <v>94006043497.789993</v>
+      </c>
+      <c r="G3">
+        <v>3.9039250000000001</v>
+      </c>
+      <c r="H3">
+        <v>28.939471000000001</v>
+      </c>
+      <c r="I3">
+        <v>28.938706999999997</v>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1772,9 +1416,8 @@
       <c r="PN3" s="2"/>
       <c r="PO3" s="2"/>
       <c r="PP3" s="2"/>
-      <c r="PQ3" s="2"/>
-    </row>
-    <row r="4" spans="1:433" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45723</v>
       </c>
@@ -1790,9 +1433,18 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="F4" s="3">
+        <v>100207888476.97</v>
+      </c>
+      <c r="G4">
+        <v>3.9066920000000001</v>
+      </c>
+      <c r="H4">
+        <v>28.959347000000001</v>
+      </c>
+      <c r="I4">
+        <v>28.958582</v>
+      </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -2216,9 +1868,8 @@
       <c r="PN4" s="2"/>
       <c r="PO4" s="2"/>
       <c r="PP4" s="2"/>
-      <c r="PQ4" s="2"/>
-    </row>
-    <row r="5" spans="1:433" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45726</v>
       </c>
@@ -2234,11 +1885,20 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F5" s="3">
+        <v>104328529968.77</v>
+      </c>
+      <c r="G5">
+        <v>3.9147759999999998</v>
+      </c>
+      <c r="H5">
+        <v>29.017364000000001</v>
+      </c>
+      <c r="I5">
+        <v>29.016597000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45727</v>
       </c>
@@ -2254,11 +1914,20 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F6" s="3">
+        <v>115810017811.7</v>
+      </c>
+      <c r="G6">
+        <v>3.9175300000000002</v>
+      </c>
+      <c r="H6">
+        <v>29.037141999999999</v>
+      </c>
+      <c r="I6">
+        <v>29.036369999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45728</v>
       </c>
@@ -2274,11 +1943,20 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F7" s="3">
+        <v>115810017811.7</v>
+      </c>
+      <c r="G7">
+        <v>3.9202710000000001</v>
+      </c>
+      <c r="H7">
+        <v>29.056823000000001</v>
+      </c>
+      <c r="I7">
+        <v>29.056047</v>
+      </c>
+    </row>
+    <row r="8" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45729</v>
       </c>
@@ -2294,11 +1972,20 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F8" s="3">
+        <v>115810017811.7</v>
+      </c>
+      <c r="G8">
+        <v>3.923054</v>
+      </c>
+      <c r="H8">
+        <v>29.076815999999997</v>
+      </c>
+      <c r="I8">
+        <v>29.076026000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45730</v>
       </c>
@@ -2314,11 +2001,20 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F9" s="3">
+        <v>75869167464.570007</v>
+      </c>
+      <c r="G9">
+        <v>3.9258150000000001</v>
+      </c>
+      <c r="H9">
+        <v>29.096644000000001</v>
+      </c>
+      <c r="I9">
+        <v>29.095846000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45733</v>
       </c>
@@ -2334,11 +2030,20 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F10" s="3">
+        <v>73721377577.87999</v>
+      </c>
+      <c r="G10">
+        <v>3.9340590000000004</v>
+      </c>
+      <c r="H10">
+        <v>29.155826000000001</v>
+      </c>
+      <c r="I10">
+        <v>29.155005000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45734</v>
       </c>
@@ -2354,11 +2059,20 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F11" s="3">
+        <v>70160021357.5</v>
+      </c>
+      <c r="G11">
+        <v>3.9367710000000002</v>
+      </c>
+      <c r="H11">
+        <v>29.175280999999998</v>
+      </c>
+      <c r="I11">
+        <v>29.174453</v>
+      </c>
+    </row>
+    <row r="12" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45735</v>
       </c>
@@ -2374,11 +2088,20 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F12" s="3">
+        <v>75551040861.01001</v>
+      </c>
+      <c r="G12">
+        <v>3.9394909999999999</v>
+      </c>
+      <c r="H12">
+        <v>29.194800999999998</v>
+      </c>
+      <c r="I12">
+        <v>29.193964000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45736</v>
       </c>
@@ -2394,11 +2117,20 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F13" s="3">
+        <v>75588869023.880005</v>
+      </c>
+      <c r="G13">
+        <v>3.942234</v>
+      </c>
+      <c r="H13">
+        <v>29.214486000000001</v>
+      </c>
+      <c r="I13">
+        <v>29.213639999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45737</v>
       </c>
@@ -2414,11 +2146,20 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F14" s="3">
+        <v>75588869023.880005</v>
+      </c>
+      <c r="G14">
+        <v>3.945004</v>
+      </c>
+      <c r="H14">
+        <v>29.234372999999998</v>
+      </c>
+      <c r="I14">
+        <v>29.233518</v>
+      </c>
+    </row>
+    <row r="15" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45741</v>
       </c>
@@ -2434,11 +2175,20 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:433" x14ac:dyDescent="0.3">
+      <c r="F15" s="3">
+        <v>75588869023.880005</v>
+      </c>
+      <c r="G15">
+        <v>3.956045</v>
+      </c>
+      <c r="H15">
+        <v>29.313617999999998</v>
+      </c>
+      <c r="I15">
+        <v>29.312726999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:432" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45742</v>
       </c>
@@ -2454,9 +2204,18 @@
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="F16" s="3">
+        <v>93385501951.540009</v>
+      </c>
+      <c r="G16">
+        <v>3.958806</v>
+      </c>
+      <c r="H16">
+        <v>29.333434</v>
+      </c>
+      <c r="I16">
+        <v>29.332533999999999</v>
+      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
@@ -2474,9 +2233,18 @@
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="F17" s="3">
+        <v>94464159917.76001</v>
+      </c>
+      <c r="G17">
+        <v>3.9615990000000001</v>
+      </c>
+      <c r="H17">
+        <v>29.353484999999999</v>
+      </c>
+      <c r="I17">
+        <v>29.352576000000003</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
@@ -2494,9 +2262,18 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="F18" s="3">
+        <v>89384774844.039993</v>
+      </c>
+      <c r="G18">
+        <v>3.9644310000000003</v>
+      </c>
+      <c r="H18">
+        <v>29.373819999999998</v>
+      </c>
+      <c r="I18">
+        <v>29.372902999999997</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
@@ -2514,9 +2291,18 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="F19" s="3">
+        <v>78782411040.940002</v>
+      </c>
+      <c r="G19">
+        <v>3.9730340000000002</v>
+      </c>
+      <c r="H19">
+        <v>29.435620999999998</v>
+      </c>
+      <c r="I19">
+        <v>29.43468</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
@@ -2534,9 +2320,18 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="F20" s="3">
+        <v>84719096832.050003</v>
+      </c>
+      <c r="G20">
+        <v>3.975949</v>
+      </c>
+      <c r="H20">
+        <v>29.456569999999999</v>
+      </c>
+      <c r="I20">
+        <v>29.455629000000002</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
@@ -2554,9 +2349,18 @@
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="F21" s="3">
+        <v>84719096832.050003</v>
+      </c>
+      <c r="G21">
+        <v>3.9816060000000002</v>
+      </c>
+      <c r="H21">
+        <v>29.497187999999998</v>
+      </c>
+      <c r="I21">
+        <v>29.496244999999998</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
@@ -2574,9 +2378,18 @@
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="F22" s="3">
+        <v>84719096832.050003</v>
+      </c>
+      <c r="G22">
+        <v>3.984483</v>
+      </c>
+      <c r="H22">
+        <v>29.517854</v>
+      </c>
+      <c r="I22">
+        <v>29.516909999999999</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
@@ -2594,9 +2407,18 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="F23" s="3">
+        <v>84719096832.050003</v>
+      </c>
+      <c r="G23">
+        <v>3.9931419999999997</v>
+      </c>
+      <c r="H23">
+        <v>29.580052999999999</v>
+      </c>
+      <c r="I23">
+        <v>29.579107</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
@@ -2614,9 +2436,18 @@
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="F24" s="3">
+        <v>88490000593.919998</v>
+      </c>
+      <c r="G24">
+        <v>3.9960810000000002</v>
+      </c>
+      <c r="H24">
+        <v>29.601172999999999</v>
+      </c>
+      <c r="I24">
+        <v>29.600225999999999</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
@@ -2634,9 +2465,18 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="F25" s="3">
+        <v>96183730885.040009</v>
+      </c>
+      <c r="G25">
+        <v>3.9989920000000003</v>
+      </c>
+      <c r="H25">
+        <v>29.622087999999998</v>
+      </c>
+      <c r="I25">
+        <v>29.62114</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
@@ -2654,9 +2494,18 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="F26" s="3">
+        <v>92944490637.790009</v>
+      </c>
+      <c r="G26">
+        <v>4.0019279999999995</v>
+      </c>
+      <c r="H26">
+        <v>29.643187000000001</v>
+      </c>
+      <c r="I26">
+        <v>29.642237000000002</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
@@ -2674,9 +2523,18 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="F27" s="3">
+        <v>74858051475.179993</v>
+      </c>
+      <c r="G27">
+        <v>4.0049359999999998</v>
+      </c>
+      <c r="H27">
+        <v>29.664814</v>
+      </c>
+      <c r="I27">
+        <v>29.663862000000002</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
@@ -2694,9 +2552,18 @@
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="F28" s="3">
+        <v>74858051475.179993</v>
+      </c>
+      <c r="G28">
+        <v>4.0154779999999999</v>
+      </c>
+      <c r="H28">
+        <v>29.740943999999999</v>
+      </c>
+      <c r="I28">
+        <v>29.739986000000002</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
@@ -2714,9 +2581,18 @@
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="F29" s="3">
+        <v>74858051475.179993</v>
+      </c>
+      <c r="G29">
+        <v>4.0192119999999996</v>
+      </c>
+      <c r="H29">
+        <v>29.767944</v>
+      </c>
+      <c r="I29">
+        <v>29.766984000000001</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
@@ -2734,9 +2610,18 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="F30" s="3">
+        <v>68335092735.150002</v>
+      </c>
+      <c r="G30">
+        <v>4.0228729999999997</v>
+      </c>
+      <c r="H30">
+        <v>29.794404</v>
+      </c>
+      <c r="I30">
+        <v>29.793440999999998</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
@@ -2754,9 +2639,18 @@
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+      <c r="F31" s="3">
+        <v>92726998957.809998</v>
+      </c>
+      <c r="G31">
+        <v>4.0392469999999996</v>
+      </c>
+      <c r="H31">
+        <v>29.912391</v>
+      </c>
+      <c r="I31">
+        <v>29.911417</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
@@ -2774,9 +2668,18 @@
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="F32" s="3">
+        <v>92726998957.809998</v>
+      </c>
+      <c r="G32">
+        <v>4.0422289999999998</v>
+      </c>
+      <c r="H32">
+        <v>29.933820000000001</v>
+      </c>
+      <c r="I32">
+        <v>29.932843999999999</v>
+      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
@@ -2794,9 +2697,18 @@
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="F33" s="3">
+        <v>73629862581.729996</v>
+      </c>
+      <c r="G33">
+        <v>4.045121</v>
+      </c>
+      <c r="H33">
+        <v>29.95458</v>
+      </c>
+      <c r="I33">
+        <v>29.953600999999999</v>
+      </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
@@ -2814,9 +2726,18 @@
       <c r="E34">
         <v>1</v>
       </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="F34" s="3">
+        <v>85679188457.059998</v>
+      </c>
+      <c r="G34">
+        <v>4.0478930000000002</v>
+      </c>
+      <c r="H34">
+        <v>29.974447000000001</v>
+      </c>
+      <c r="I34">
+        <v>29.973465000000001</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
@@ -2834,9 +2755,18 @@
       <c r="E35">
         <v>1</v>
       </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="F35" s="3">
+        <v>85679188457.059998</v>
+      </c>
+      <c r="G35">
+        <v>4.0507229999999996</v>
+      </c>
+      <c r="H35">
+        <v>29.994745999999999</v>
+      </c>
+      <c r="I35">
+        <v>29.993762</v>
+      </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
@@ -2854,9 +2784,18 @@
       <c r="E36">
         <v>1</v>
       </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="F36" s="3">
+        <v>85679188457.059998</v>
+      </c>
+      <c r="G36">
+        <v>4.0595309999999998</v>
+      </c>
+      <c r="H36">
+        <v>30.057993</v>
+      </c>
+      <c r="I36">
+        <v>30.057008000000003</v>
+      </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
@@ -2874,9 +2813,18 @@
       <c r="E37">
         <v>1</v>
       </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="F37" s="3">
+        <v>72422363700.110001</v>
+      </c>
+      <c r="G37">
+        <v>4.0624019999999996</v>
+      </c>
+      <c r="H37">
+        <v>30.078589000000001</v>
+      </c>
+      <c r="I37">
+        <v>30.077601999999999</v>
+      </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
@@ -2894,9 +2842,18 @@
       <c r="E38">
         <v>1</v>
       </c>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="F38" s="3">
+        <v>78064909332.610001</v>
+      </c>
+      <c r="G38">
+        <v>4.0652089999999994</v>
+      </c>
+      <c r="H38">
+        <v>30.098710000000001</v>
+      </c>
+      <c r="I38">
+        <v>30.097721</v>
+      </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
@@ -2914,9 +2871,18 @@
       <c r="E39">
         <v>1</v>
       </c>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="F39" s="3">
+        <v>78867328808.080002</v>
+      </c>
+      <c r="G39">
+        <v>4.0793759999999999</v>
+      </c>
+      <c r="H39">
+        <v>30.200292000000001</v>
+      </c>
+      <c r="I39">
+        <v>30.199300000000001</v>
+      </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
@@ -2934,9 +2900,18 @@
       <c r="E40">
         <v>1</v>
       </c>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+      <c r="F40" s="3">
+        <v>79616729452.580002</v>
+      </c>
+      <c r="G40">
+        <v>4.0823109999999998</v>
+      </c>
+      <c r="H40">
+        <v>30.221360000000001</v>
+      </c>
+      <c r="I40">
+        <v>30.220367999999997</v>
+      </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
@@ -2954,9 +2929,18 @@
       <c r="E41">
         <v>1</v>
       </c>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+      <c r="F41" s="3">
+        <v>77394186853.779999</v>
+      </c>
+      <c r="G41">
+        <v>4.0851740000000003</v>
+      </c>
+      <c r="H41">
+        <v>30.241893000000001</v>
+      </c>
+      <c r="I41">
+        <v>30.2409</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
@@ -2974,9 +2958,18 @@
       <c r="E42">
         <v>1</v>
       </c>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+      <c r="F42" s="3">
+        <v>77394186853.779999</v>
+      </c>
+      <c r="G42">
+        <v>4.0880659999999995</v>
+      </c>
+      <c r="H42">
+        <v>30.262640000000001</v>
+      </c>
+      <c r="I42">
+        <v>30.261645999999999</v>
+      </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
@@ -2994,9 +2987,18 @@
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+      <c r="F43" s="3">
+        <v>77394186853.779999</v>
+      </c>
+      <c r="G43">
+        <v>4.0909520000000006</v>
+      </c>
+      <c r="H43">
+        <v>30.283338000000001</v>
+      </c>
+      <c r="I43">
+        <v>30.282343000000001</v>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
@@ -3014,9 +3016,18 @@
       <c r="E44">
         <v>1</v>
       </c>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+      <c r="F44" s="3">
+        <v>68799323030.020004</v>
+      </c>
+      <c r="G44">
+        <v>4.0998570000000001</v>
+      </c>
+      <c r="H44">
+        <v>30.347259999999999</v>
+      </c>
+      <c r="I44">
+        <v>30.346263999999998</v>
+      </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
@@ -3034,9 +3045,18 @@
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+      <c r="F45" s="3">
+        <v>70328536518.720001</v>
+      </c>
+      <c r="G45">
+        <v>4.1027329999999997</v>
+      </c>
+      <c r="H45">
+        <v>30.367881000000001</v>
+      </c>
+      <c r="I45">
+        <v>30.366883999999999</v>
+      </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
@@ -3054,9 +3074,18 @@
       <c r="E46">
         <v>1</v>
       </c>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+      <c r="F46" s="3">
+        <v>77896092151.880005</v>
+      </c>
+      <c r="G46">
+        <v>4.1056080000000001</v>
+      </c>
+      <c r="H46">
+        <v>30.388493999999998</v>
+      </c>
+      <c r="I46">
+        <v>30.387495999999999</v>
+      </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
@@ -3074,9 +3103,18 @@
       <c r="E47">
         <v>1</v>
       </c>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+      <c r="F47" s="3">
+        <v>77896092151.880005</v>
+      </c>
+      <c r="G47">
+        <v>4.1084139999999998</v>
+      </c>
+      <c r="H47">
+        <v>30.408597</v>
+      </c>
+      <c r="I47">
+        <v>30.407598</v>
+      </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
@@ -3094,9 +3132,18 @@
       <c r="E48">
         <v>1</v>
       </c>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+      <c r="F48" s="3">
+        <v>77896092151.880005</v>
+      </c>
+      <c r="G48">
+        <v>4.1112890000000002</v>
+      </c>
+      <c r="H48">
+        <v>30.429209</v>
+      </c>
+      <c r="I48">
+        <v>30.42821</v>
+      </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
@@ -3114,9 +3161,18 @@
       <c r="E49">
         <v>1</v>
       </c>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
+      <c r="F49" s="3">
+        <v>77896092151.880005</v>
+      </c>
+      <c r="G49">
+        <v>4.1199939999999993</v>
+      </c>
+      <c r="H49">
+        <v>30.491628000000002</v>
+      </c>
+      <c r="I49">
+        <v>30.490627</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
@@ -3134,9 +3190,18 @@
       <c r="E50">
         <v>1</v>
       </c>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+      <c r="F50" s="3">
+        <v>77896092151.880005</v>
+      </c>
+      <c r="G50">
+        <v>4.1229339999999999</v>
+      </c>
+      <c r="H50">
+        <v>30.512717000000002</v>
+      </c>
+      <c r="I50">
+        <v>30.511716</v>
+      </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
@@ -3154,9 +3219,18 @@
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+      <c r="F51" s="3">
+        <v>70133367897.619995</v>
+      </c>
+      <c r="G51">
+        <v>4.1258289999999995</v>
+      </c>
+      <c r="H51">
+        <v>30.533472000000003</v>
+      </c>
+      <c r="I51">
+        <v>30.532471000000001</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
@@ -3174,9 +3248,18 @@
       <c r="E52">
         <v>1</v>
       </c>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
+      <c r="F52" s="3">
+        <v>72265539040.790009</v>
+      </c>
+      <c r="G52">
+        <v>4.128698</v>
+      </c>
+      <c r="H52">
+        <v>30.554036</v>
+      </c>
+      <c r="I52">
+        <v>30.553034</v>
+      </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
@@ -3194,9 +3277,18 @@
       <c r="E53">
         <v>1</v>
       </c>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+      <c r="F53" s="3">
+        <v>92696426870.300003</v>
+      </c>
+      <c r="G53">
+        <v>4.1315309999999998</v>
+      </c>
+      <c r="H53">
+        <v>30.574332999999999</v>
+      </c>
+      <c r="I53">
+        <v>30.573330000000002</v>
+      </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
@@ -3214,9 +3306,18 @@
       <c r="E54">
         <v>1</v>
       </c>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
+      <c r="F54" s="3">
+        <v>80893807943.630005</v>
+      </c>
+      <c r="G54">
+        <v>4.1403909999999993</v>
+      </c>
+      <c r="H54">
+        <v>30.637881</v>
+      </c>
+      <c r="I54">
+        <v>30.636876000000001</v>
+      </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
@@ -3234,9 +3335,18 @@
       <c r="E55">
         <v>1</v>
       </c>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
+      <c r="F55" s="3">
+        <v>71771365388.070007</v>
+      </c>
+      <c r="G55">
+        <v>4.143332</v>
+      </c>
+      <c r="H55">
+        <v>30.658969000000003</v>
+      </c>
+      <c r="I55">
+        <v>30.657962999999999</v>
+      </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
@@ -3254,9 +3364,18 @@
       <c r="E56">
         <v>1</v>
       </c>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+      <c r="F56" s="3">
+        <v>71771365388.070007</v>
+      </c>
+      <c r="G56">
+        <v>4.1462470000000007</v>
+      </c>
+      <c r="H56">
+        <v>30.679863000000001</v>
+      </c>
+      <c r="I56">
+        <v>30.678856</v>
+      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
@@ -3274,9 +3393,18 @@
       <c r="E57">
         <v>1</v>
       </c>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
+      <c r="F57" s="3">
+        <v>71771365388.070007</v>
+      </c>
+      <c r="G57">
+        <v>4.149133</v>
+      </c>
+      <c r="H57">
+        <v>30.700543000000003</v>
+      </c>
+      <c r="I57">
+        <v>30.699534</v>
+      </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
@@ -3294,9 +3422,18 @@
       <c r="E58">
         <v>1</v>
       </c>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
+      <c r="F58" s="3">
+        <v>78859882454.839996</v>
+      </c>
+      <c r="G58">
+        <v>4.1520330000000003</v>
+      </c>
+      <c r="H58">
+        <v>30.721328</v>
+      </c>
+      <c r="I58">
+        <v>30.720317999999999</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
@@ -3314,9 +3451,18 @@
       <c r="E59">
         <v>1</v>
       </c>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+      <c r="F59" s="3">
+        <v>84125677244.830002</v>
+      </c>
+      <c r="G59">
+        <v>4.1608919999999996</v>
+      </c>
+      <c r="H59">
+        <v>30.784851</v>
+      </c>
+      <c r="I59">
+        <v>30.783839</v>
+      </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
@@ -3334,9 +3480,18 @@
       <c r="E60">
         <v>1</v>
       </c>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+      <c r="F60" s="3">
+        <v>81479182137.399994</v>
+      </c>
+      <c r="G60">
+        <v>4.1639059999999999</v>
+      </c>
+      <c r="H60">
+        <v>30.806472000000003</v>
+      </c>
+      <c r="I60">
+        <v>30.805458999999999</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
@@ -3354,9 +3509,18 @@
       <c r="E61">
         <v>1</v>
       </c>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+      <c r="F61" s="3">
+        <v>81479182137.399994</v>
+      </c>
+      <c r="G61">
+        <v>4.1669080000000003</v>
+      </c>
+      <c r="H61">
+        <v>30.828005000000001</v>
+      </c>
+      <c r="I61">
+        <v>30.826991999999997</v>
+      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
@@ -3374,9 +3538,18 @@
       <c r="E62">
         <v>1</v>
       </c>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="F62" s="3">
+        <v>81479182137.399994</v>
+      </c>
+      <c r="G62">
+        <v>4.1698370000000002</v>
+      </c>
+      <c r="H62">
+        <v>30.848996</v>
+      </c>
+      <c r="I62">
+        <v>30.847982999999999</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
@@ -3394,9 +3567,18 @@
       <c r="E63">
         <v>1</v>
       </c>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="F63" s="3">
+        <v>81479182137.399994</v>
+      </c>
+      <c r="G63">
+        <v>4.172809</v>
+      </c>
+      <c r="H63">
+        <v>30.870305999999999</v>
+      </c>
+      <c r="I63">
+        <v>30.869293000000003</v>
+      </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
@@ -3414,9 +3596,18 @@
       <c r="E64">
         <v>1</v>
       </c>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
+      <c r="F64" s="3">
+        <v>81479182137.399994</v>
+      </c>
+      <c r="G64">
+        <v>4.1815319999999998</v>
+      </c>
+      <c r="H64">
+        <v>30.932798999999999</v>
+      </c>
+      <c r="I64">
+        <v>30.931782999999999</v>
+      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
@@ -3434,9 +3625,18 @@
       <c r="E65">
         <v>1</v>
       </c>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="F65" s="3">
+        <v>67195869535.620003</v>
+      </c>
+      <c r="G65">
+        <v>4.1846009999999998</v>
+      </c>
+      <c r="H65">
+        <v>30.954826000000001</v>
+      </c>
+      <c r="I65">
+        <v>30.953809</v>
+      </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
@@ -3454,9 +3654,18 @@
       <c r="E66">
         <v>1</v>
       </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+      <c r="F66" s="3">
+        <v>78673035127.470001</v>
+      </c>
+      <c r="G66">
+        <v>4.1877330000000006</v>
+      </c>
+      <c r="H66">
+        <v>30.977316999999999</v>
+      </c>
+      <c r="I66">
+        <v>30.976298999999997</v>
+      </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
@@ -3474,9 +3683,18 @@
       <c r="E67">
         <v>1</v>
       </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="F67" s="3">
+        <v>75197893887.589996</v>
+      </c>
+      <c r="G67">
+        <v>4.1909799999999997</v>
+      </c>
+      <c r="H67">
+        <v>31.000654999999998</v>
+      </c>
+      <c r="I67">
+        <v>30.999635999999999</v>
+      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
@@ -3494,9 +3712,18 @@
       <c r="E68">
         <v>1</v>
       </c>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
+      <c r="F68" s="3">
+        <v>78464068635.730011</v>
+      </c>
+      <c r="G68">
+        <v>4.1942120000000003</v>
+      </c>
+      <c r="H68">
+        <v>31.023881000000003</v>
+      </c>
+      <c r="I68">
+        <v>31.022861000000002</v>
+      </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
@@ -3514,9 +3741,18 @@
       <c r="E69">
         <v>1</v>
       </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+      <c r="F69" s="3">
+        <v>66105303399.37999</v>
+      </c>
+      <c r="G69">
+        <v>4.2069020000000004</v>
+      </c>
+      <c r="H69">
+        <v>31.115016999999998</v>
+      </c>
+      <c r="I69">
+        <v>31.113996999999998</v>
+      </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
@@ -3534,9 +3770,18 @@
       <c r="E70">
         <v>1</v>
       </c>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="F70" s="3">
+        <v>66105303399.37999</v>
+      </c>
+      <c r="G70">
+        <v>4.2101679999999995</v>
+      </c>
+      <c r="H70">
+        <v>31.138491000000002</v>
+      </c>
+      <c r="I70">
+        <v>31.13747</v>
+      </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
@@ -3554,9 +3799,18 @@
       <c r="E71">
         <v>1</v>
       </c>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="F71" s="3">
+        <v>66105303399.37999</v>
+      </c>
+      <c r="G71">
+        <v>4.2135370000000005</v>
+      </c>
+      <c r="H71">
+        <v>31.162724999999998</v>
+      </c>
+      <c r="I71">
+        <v>31.161703000000003</v>
+      </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
@@ -3574,9 +3828,18 @@
       <c r="E72">
         <v>1</v>
       </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="F72" s="3">
+        <v>82826236007.190002</v>
+      </c>
+      <c r="G72">
+        <v>4.2263630000000001</v>
+      </c>
+      <c r="H72">
+        <v>31.254840000000002</v>
+      </c>
+      <c r="I72">
+        <v>31.253812000000003</v>
+      </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
@@ -3594,9 +3857,18 @@
       <c r="E73">
         <v>1</v>
       </c>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
+      <c r="F73" s="3">
+        <v>81558483177</v>
+      </c>
+      <c r="G73">
+        <v>4.2294340000000004</v>
+      </c>
+      <c r="H73">
+        <v>31.276863000000002</v>
+      </c>
+      <c r="I73">
+        <v>31.275832999999999</v>
+      </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
@@ -3614,9 +3886,18 @@
       <c r="E74">
         <v>1</v>
       </c>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
+      <c r="F74" s="3">
+        <v>97018474712.589996</v>
+      </c>
+      <c r="G74">
+        <v>4.2326819999999996</v>
+      </c>
+      <c r="H74">
+        <v>31.300194999999999</v>
+      </c>
+      <c r="I74">
+        <v>31.299164000000001</v>
+      </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
@@ -3634,9 +3915,18 @@
       <c r="E75">
         <v>1</v>
       </c>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
+      <c r="F75" s="3">
+        <v>82490083386.709991</v>
+      </c>
+      <c r="G75">
+        <v>4.2358959999999994</v>
+      </c>
+      <c r="H75">
+        <v>31.323273</v>
+      </c>
+      <c r="I75">
+        <v>31.322239</v>
+      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
@@ -3654,9 +3944,18 @@
       <c r="E76">
         <v>1</v>
       </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
+      <c r="F76" s="3">
+        <v>76030148088.639999</v>
+      </c>
+      <c r="G76">
+        <v>4.2391180000000004</v>
+      </c>
+      <c r="H76">
+        <v>31.346412000000001</v>
+      </c>
+      <c r="I76">
+        <v>31.345376000000002</v>
+      </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
@@ -3674,9 +3973,18 @@
       <c r="E77">
         <v>1</v>
       </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="F77" s="3">
+        <v>76030148088.639999</v>
+      </c>
+      <c r="G77">
+        <v>4.2489520000000001</v>
+      </c>
+      <c r="H77">
+        <v>31.417062999999999</v>
+      </c>
+      <c r="I77">
+        <v>31.416024</v>
+      </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
@@ -3694,9 +4002,18 @@
       <c r="E78">
         <v>1</v>
       </c>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
+      <c r="F78" s="3">
+        <v>76030148088.639999</v>
+      </c>
+      <c r="G78">
+        <v>4.2521779999999998</v>
+      </c>
+      <c r="H78">
+        <v>31.440225999999999</v>
+      </c>
+      <c r="I78">
+        <v>31.439186000000003</v>
+      </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
@@ -3714,9 +4031,18 @@
       <c r="E79">
         <v>1</v>
       </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
+      <c r="F79" s="3">
+        <v>68767995191.580002</v>
+      </c>
+      <c r="G79">
+        <v>4.2552409999999998</v>
+      </c>
+      <c r="H79">
+        <v>31.462184000000001</v>
+      </c>
+      <c r="I79">
+        <v>31.461143</v>
+      </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
@@ -3734,9 +4060,18 @@
       <c r="E80">
         <v>1</v>
       </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
+      <c r="F80" s="3">
+        <v>75889594233.630005</v>
+      </c>
+      <c r="G80">
+        <v>4.258267</v>
+      </c>
+      <c r="H80">
+        <v>31.483866000000003</v>
+      </c>
+      <c r="I80">
+        <v>31.482825000000002</v>
+      </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
@@ -3754,9 +4089,18 @@
       <c r="E81">
         <v>1</v>
       </c>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
+      <c r="F81" s="3">
+        <v>79563371910.339996</v>
+      </c>
+      <c r="G81">
+        <v>4.2612329999999998</v>
+      </c>
+      <c r="H81">
+        <v>31.505108</v>
+      </c>
+      <c r="I81">
+        <v>31.504065999999998</v>
+      </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
@@ -3774,9 +4118,18 @@
       <c r="E82">
         <v>1</v>
       </c>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
+      <c r="F82" s="3">
+        <v>87696098974.360001</v>
+      </c>
+      <c r="G82">
+        <v>4.2700389999999997</v>
+      </c>
+      <c r="H82">
+        <v>31.568134999999998</v>
+      </c>
+      <c r="I82">
+        <v>31.567091999999999</v>
+      </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
@@ -3794,9 +4147,18 @@
       <c r="E83">
         <v>1</v>
       </c>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
+      <c r="F83" s="3">
+        <v>69871219967.170013</v>
+      </c>
+      <c r="G83">
+        <v>4.2729399999999993</v>
+      </c>
+      <c r="H83">
+        <v>31.588891</v>
+      </c>
+      <c r="I83">
+        <v>31.587847</v>
+      </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
@@ -3814,9 +4176,18 @@
       <c r="E84">
         <v>1</v>
       </c>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
+      <c r="F84" s="3">
+        <v>69871219967.170013</v>
+      </c>
+      <c r="G84">
+        <v>4.2789190000000001</v>
+      </c>
+      <c r="H84">
+        <v>31.631708</v>
+      </c>
+      <c r="I84">
+        <v>31.630662000000001</v>
+      </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
@@ -3834,9 +4205,18 @@
       <c r="E85">
         <v>1</v>
       </c>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
+      <c r="F85" s="3">
+        <v>69871219967.170013</v>
+      </c>
+      <c r="G85">
+        <v>4.2818239999999994</v>
+      </c>
+      <c r="H85">
+        <v>31.65249</v>
+      </c>
+      <c r="I85">
+        <v>31.651443</v>
+      </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
@@ -3854,9 +4234,18 @@
       <c r="E86">
         <v>1</v>
       </c>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
+      <c r="F86" s="3">
+        <v>73506155095.790009</v>
+      </c>
+      <c r="G86">
+        <v>4.2892960000000002</v>
+      </c>
+      <c r="H86">
+        <v>31.705638999999998</v>
+      </c>
+      <c r="I86">
+        <v>31.704591000000001</v>
+      </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
@@ -3874,9 +4263,18 @@
       <c r="E87">
         <v>1</v>
       </c>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
+      <c r="F87" s="3">
+        <v>77429218127.270004</v>
+      </c>
+      <c r="G87">
+        <v>4.2918419999999999</v>
+      </c>
+      <c r="H87">
+        <v>31.723763999999999</v>
+      </c>
+      <c r="I87">
+        <v>31.722716000000002</v>
+      </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
@@ -3894,9 +4292,18 @@
       <c r="E88">
         <v>1</v>
       </c>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
+      <c r="F88" s="3">
+        <v>85405245612.449997</v>
+      </c>
+      <c r="G88">
+        <v>4.2946559999999998</v>
+      </c>
+      <c r="H88">
+        <v>31.743869999999998</v>
+      </c>
+      <c r="I88">
+        <v>31.742820999999999</v>
+      </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
@@ -3914,9 +4321,18 @@
       <c r="E89">
         <v>1</v>
       </c>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
+      <c r="F89" s="3">
+        <v>88073084710.360001</v>
+      </c>
+      <c r="G89">
+        <v>4.2978180000000004</v>
+      </c>
+      <c r="H89">
+        <v>31.766543000000002</v>
+      </c>
+      <c r="I89">
+        <v>31.765492999999999</v>
+      </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
@@ -3934,9 +4350,18 @@
       <c r="E90">
         <v>1</v>
       </c>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
+      <c r="F90" s="3">
+        <v>86138614917.589996</v>
+      </c>
+      <c r="G90">
+        <v>4.3009179999999994</v>
+      </c>
+      <c r="H90">
+        <v>31.78876</v>
+      </c>
+      <c r="I90">
+        <v>31.787710000000001</v>
+      </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
@@ -3954,9 +4379,18 @@
       <c r="E91">
         <v>1</v>
       </c>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
+      <c r="F91" s="3">
+        <v>86138614917.589996</v>
+      </c>
+      <c r="G91">
+        <v>4.3111940000000004</v>
+      </c>
+      <c r="H91">
+        <v>31.862611000000001</v>
+      </c>
+      <c r="I91">
+        <v>31.861558000000002</v>
+      </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
@@ -3974,9 +4408,18 @@
       <c r="E92">
         <v>1</v>
       </c>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
+      <c r="F92" s="3">
+        <v>86138614917.589996</v>
+      </c>
+      <c r="G92">
+        <v>4.3154810000000001</v>
+      </c>
+      <c r="H92">
+        <v>31.893591000000001</v>
+      </c>
+      <c r="I92">
+        <v>31.892538999999999</v>
+      </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
@@ -3994,9 +4437,18 @@
       <c r="E93">
         <v>1</v>
       </c>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
+      <c r="F93" s="3">
+        <v>75226524788.839996</v>
+      </c>
+      <c r="G93">
+        <v>4.3208029999999997</v>
+      </c>
+      <c r="H93">
+        <v>31.932221000000002</v>
+      </c>
+      <c r="I93">
+        <v>31.931167000000002</v>
+      </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
@@ -4014,9 +4466,18 @@
       <c r="E94">
         <v>1</v>
       </c>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
+      <c r="F94" s="3">
+        <v>74778079332.940002</v>
+      </c>
+      <c r="G94">
+        <v>4.325145</v>
+      </c>
+      <c r="H94">
+        <v>31.963609000000002</v>
+      </c>
+      <c r="I94">
+        <v>31.962553</v>
+      </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
@@ -4034,9 +4495,18 @@
       <c r="E95">
         <v>1</v>
       </c>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
+      <c r="F95" s="3">
+        <v>85465636766.679993</v>
+      </c>
+      <c r="G95">
+        <v>4.3289949999999999</v>
+      </c>
+      <c r="H95">
+        <v>31.991358000000002</v>
+      </c>
+      <c r="I95">
+        <v>31.990300999999999</v>
+      </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
@@ -4054,9 +4524,18 @@
       <c r="E96">
         <v>1</v>
       </c>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
+      <c r="F96" s="3">
+        <v>91604774971.099991</v>
+      </c>
+      <c r="G96">
+        <v>4.3398560000000002</v>
+      </c>
+      <c r="H96">
+        <v>32.069504999999999</v>
+      </c>
+      <c r="I96">
+        <v>32.068443000000002</v>
+      </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
@@ -4074,9 +4553,18 @@
       <c r="E97">
         <v>1</v>
       </c>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
+      <c r="F97" s="3">
+        <v>102764248775.03999</v>
+      </c>
+      <c r="G97">
+        <v>4.3436760000000003</v>
+      </c>
+      <c r="H97">
+        <v>32.097026999999997</v>
+      </c>
+      <c r="I97">
+        <v>32.095965</v>
+      </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
@@ -4094,9 +4582,18 @@
       <c r="E98">
         <v>1</v>
       </c>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
+      <c r="F98" s="3">
+        <v>102764248775.03999</v>
+      </c>
+      <c r="G98">
+        <v>4.3476270000000001</v>
+      </c>
+      <c r="H98">
+        <v>32.125520000000002</v>
+      </c>
+      <c r="I98">
+        <v>32.124455999999995</v>
+      </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
@@ -4114,9 +4611,18 @@
       <c r="E99">
         <v>1</v>
       </c>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3"/>
+      <c r="F99" s="3">
+        <v>102764248775.03999</v>
+      </c>
+      <c r="G99">
+        <v>4.3511869999999995</v>
+      </c>
+      <c r="H99">
+        <v>32.151119999999999</v>
+      </c>
+      <c r="I99">
+        <v>32.150057000000004</v>
+      </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
@@ -4134,9 +4640,18 @@
       <c r="E100">
         <v>1</v>
       </c>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3"/>
+      <c r="F100" s="3">
+        <v>84961096827.700012</v>
+      </c>
+      <c r="G100">
+        <v>4.3548810000000007</v>
+      </c>
+      <c r="H100">
+        <v>32.177712999999997</v>
+      </c>
+      <c r="I100">
+        <v>32.176650000000002</v>
+      </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
@@ -4154,9 +4669,18 @@
       <c r="E101">
         <v>1</v>
       </c>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
+      <c r="F101" s="3">
+        <v>76418168397.740005</v>
+      </c>
+      <c r="G101">
+        <v>4.3653420000000001</v>
+      </c>
+      <c r="H101">
+        <v>32.252888999999996</v>
+      </c>
+      <c r="I101">
+        <v>32.251823000000002</v>
+      </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
@@ -4174,9 +4698,18 @@
       <c r="E102">
         <v>1</v>
       </c>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
+      <c r="F102" s="3">
+        <v>75699039683.279999</v>
+      </c>
+      <c r="G102">
+        <v>4.3688840000000004</v>
+      </c>
+      <c r="H102">
+        <v>32.278349999999996</v>
+      </c>
+      <c r="I102">
+        <v>32.277282999999997</v>
+      </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
@@ -4194,9 +4727,18 @@
       <c r="E103">
         <v>1</v>
       </c>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
+      <c r="F103" s="3">
+        <v>78929050361.079987</v>
+      </c>
+      <c r="G103">
+        <v>4.3723619999999999</v>
+      </c>
+      <c r="H103">
+        <v>32.303339999999999</v>
+      </c>
+      <c r="I103">
+        <v>32.302273</v>
+      </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
@@ -4214,9 +4756,18 @@
       <c r="E104">
         <v>1</v>
       </c>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="3"/>
+      <c r="F104" s="3">
+        <v>77187497085.600006</v>
+      </c>
+      <c r="G104">
+        <v>4.376099</v>
+      </c>
+      <c r="H104">
+        <v>32.330238000000001</v>
+      </c>
+      <c r="I104">
+        <v>32.329169999999998</v>
+      </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
@@ -4234,9 +4785,18 @@
       <c r="E105">
         <v>1</v>
       </c>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="3"/>
+      <c r="F105" s="3">
+        <v>77187497085.600006</v>
+      </c>
+      <c r="G105">
+        <v>4.3804509999999999</v>
+      </c>
+      <c r="H105">
+        <v>32.36168</v>
+      </c>
+      <c r="I105">
+        <v>32.360610999999999</v>
+      </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
@@ -4254,9 +4814,18 @@
       <c r="E106">
         <v>1</v>
       </c>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="3"/>
+      <c r="F106" s="3">
+        <v>77187497085.600006</v>
+      </c>
+      <c r="G106">
+        <v>4.3941429999999997</v>
+      </c>
+      <c r="H106">
+        <v>32.460701</v>
+      </c>
+      <c r="I106">
+        <v>32.459628000000002</v>
+      </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
@@ -4274,9 +4843,18 @@
       <c r="E107">
         <v>1</v>
       </c>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
-      <c r="I107" s="3"/>
+      <c r="F107" s="3">
+        <v>77187497085.599991</v>
+      </c>
+      <c r="G107">
+        <v>4.3989849999999997</v>
+      </c>
+      <c r="H107">
+        <v>32.495759999999997</v>
+      </c>
+      <c r="I107">
+        <v>32.494686000000002</v>
+      </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
@@ -4294,9 +4872,18 @@
       <c r="E108">
         <v>1</v>
       </c>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
-      <c r="I108" s="3"/>
+      <c r="F108" s="3">
+        <v>84909334011.019989</v>
+      </c>
+      <c r="G108">
+        <v>4.4038590000000006</v>
+      </c>
+      <c r="H108">
+        <v>32.531052000000003</v>
+      </c>
+      <c r="I108">
+        <v>32.529975</v>
+      </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
@@ -4314,9 +4901,18 @@
       <c r="E109">
         <v>1</v>
       </c>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
+      <c r="F109" s="3">
+        <v>82044827944.759995</v>
+      </c>
+      <c r="G109">
+        <v>4.4089840000000002</v>
+      </c>
+      <c r="H109">
+        <v>32.568191999999996</v>
+      </c>
+      <c r="I109">
+        <v>32.567112999999999</v>
+      </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
@@ -4334,9 +4930,18 @@
       <c r="E110">
         <v>1</v>
       </c>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
+      <c r="F110" s="3">
+        <v>87018830730.680008</v>
+      </c>
+      <c r="G110">
+        <v>4.429951</v>
+      </c>
+      <c r="H110">
+        <v>32.720202</v>
+      </c>
+      <c r="I110">
+        <v>32.719116</v>
+      </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
@@ -4354,9 +4959,18 @@
       <c r="E111">
         <v>1</v>
       </c>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
+      <c r="F111" s="3">
+        <v>87018830730.680008</v>
+      </c>
+      <c r="G111">
+        <v>4.4343969999999997</v>
+      </c>
+      <c r="H111">
+        <v>32.752319999999997</v>
+      </c>
+      <c r="I111">
+        <v>32.751232000000002</v>
+      </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
@@ -4374,9 +4988,18 @@
       <c r="E112">
         <v>1</v>
       </c>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
+      <c r="F112" s="3">
+        <v>87018830730.680008</v>
+      </c>
+      <c r="G112">
+        <v>4.4382809999999999</v>
+      </c>
+      <c r="H112">
+        <v>32.780285000000006</v>
+      </c>
+      <c r="I112">
+        <v>32.779195000000001</v>
+      </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
@@ -4394,9 +5017,18 @@
       <c r="E113">
         <v>1</v>
       </c>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
+      <c r="F113" s="3">
+        <v>87018830730.680008</v>
+      </c>
+      <c r="G113">
+        <v>4.4424229999999998</v>
+      </c>
+      <c r="H113">
+        <v>32.810155000000002</v>
+      </c>
+      <c r="I113">
+        <v>32.809063000000002</v>
+      </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
@@ -4414,9 +5046,18 @@
       <c r="E114">
         <v>1</v>
       </c>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
+      <c r="F114" s="3">
+        <v>108933193670.65001</v>
+      </c>
+      <c r="G114">
+        <v>4.4471319999999999</v>
+      </c>
+      <c r="H114">
+        <v>32.844214999999998</v>
+      </c>
+      <c r="I114">
+        <v>32.843120999999996</v>
+      </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
@@ -4434,9 +5075,18 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
+      <c r="F115" s="3">
+        <v>85425290018.12999</v>
+      </c>
+      <c r="G115">
+        <v>4.4595910000000005</v>
+      </c>
+      <c r="H115">
+        <v>32.934059999999995</v>
+      </c>
+      <c r="I115">
+        <v>32.932961999999996</v>
+      </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
@@ -4454,9 +5104,18 @@
       <c r="E116">
         <v>1</v>
       </c>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
+      <c r="F116" s="3">
+        <v>94133316001.809998</v>
+      </c>
+      <c r="G116">
+        <v>4.4646980000000003</v>
+      </c>
+      <c r="H116">
+        <v>32.971048000000003</v>
+      </c>
+      <c r="I116">
+        <v>32.969949</v>
+      </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
@@ -4474,9 +5133,18 @@
       <c r="E117">
         <v>1</v>
       </c>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
+      <c r="F117" s="3">
+        <v>90926896135.639999</v>
+      </c>
+      <c r="G117">
+        <v>4.4696419999999994</v>
+      </c>
+      <c r="H117">
+        <v>33.006830000000001</v>
+      </c>
+      <c r="I117">
+        <v>33.005729000000002</v>
+      </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
@@ -4494,9 +5162,18 @@
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
+      <c r="F118" s="3">
+        <v>90738528399.479996</v>
+      </c>
+      <c r="G118">
+        <v>4.474469</v>
+      </c>
+      <c r="H118">
+        <v>33.041750999999998</v>
+      </c>
+      <c r="I118">
+        <v>33.040648000000004</v>
+      </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
@@ -4514,9 +5191,18 @@
       <c r="E119">
         <v>1</v>
       </c>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
+      <c r="F119" s="3">
+        <v>90738528399.479996</v>
+      </c>
+      <c r="G119">
+        <v>4.4794239999999999</v>
+      </c>
+      <c r="H119">
+        <v>33.077615999999999</v>
+      </c>
+      <c r="I119">
+        <v>33.076512999999998</v>
+      </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
@@ -4534,9 +5220,18 @@
       <c r="E120">
         <v>1</v>
       </c>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
+      <c r="F120" s="3">
+        <v>90738528399.479996</v>
+      </c>
+      <c r="G120">
+        <v>4.4941300000000002</v>
+      </c>
+      <c r="H120">
+        <v>33.184031000000004</v>
+      </c>
+      <c r="I120">
+        <v>33.182924</v>
+      </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
@@ -4554,9 +5249,18 @@
       <c r="E121">
         <v>1</v>
       </c>
-      <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="3"/>
+      <c r="F121" s="3">
+        <v>88329580945.139999</v>
+      </c>
+      <c r="G121">
+        <v>4.4991659999999998</v>
+      </c>
+      <c r="H121">
+        <v>33.220491000000003</v>
+      </c>
+      <c r="I121">
+        <v>33.219381999999996</v>
+      </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
@@ -4574,9 +5278,18 @@
       <c r="E122">
         <v>1</v>
       </c>
-      <c r="G122" s="3"/>
-      <c r="H122" s="3"/>
-      <c r="I122" s="3"/>
+      <c r="F122" s="3">
+        <v>91531515957.209991</v>
+      </c>
+      <c r="G122">
+        <v>4.5041499999999992</v>
+      </c>
+      <c r="H122">
+        <v>33.256565000000002</v>
+      </c>
+      <c r="I122">
+        <v>33.255455000000005</v>
+      </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
@@ -4594,9 +5307,18 @@
       <c r="E123">
         <v>1</v>
       </c>
-      <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
-      <c r="I123" s="3"/>
+      <c r="F123" s="3">
+        <v>99362997127.740005</v>
+      </c>
+      <c r="G123">
+        <v>4.5089809999999995</v>
+      </c>
+      <c r="H123">
+        <v>33.291505999999998</v>
+      </c>
+      <c r="I123">
+        <v>33.290393999999999</v>
+      </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
@@ -4614,9 +5336,18 @@
       <c r="E124">
         <v>1</v>
       </c>
-      <c r="G124" s="3"/>
-      <c r="H124" s="3"/>
-      <c r="I124" s="3"/>
+      <c r="F124" s="3">
+        <v>96138023769.720001</v>
+      </c>
+      <c r="G124">
+        <v>4.5139719999999999</v>
+      </c>
+      <c r="H124">
+        <v>33.327629000000002</v>
+      </c>
+      <c r="I124">
+        <v>33.326516000000005</v>
+      </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
@@ -4634,9 +5365,18 @@
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="G125" s="3"/>
-      <c r="H125" s="3"/>
-      <c r="I125" s="3"/>
+      <c r="F125" s="3">
+        <v>91384260439.270004</v>
+      </c>
+      <c r="G125">
+        <v>4.5297330000000002</v>
+      </c>
+      <c r="H125">
+        <v>33.441796000000004</v>
+      </c>
+      <c r="I125">
+        <v>33.440680999999998</v>
+      </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
@@ -4654,9 +5394,18 @@
       <c r="E126">
         <v>1</v>
       </c>
-      <c r="G126" s="3"/>
-      <c r="H126" s="3"/>
-      <c r="I126" s="3"/>
+      <c r="F126" s="3">
+        <v>91384260439.270004</v>
+      </c>
+      <c r="G126">
+        <v>4.5351300000000005</v>
+      </c>
+      <c r="H126">
+        <v>33.480908999999997</v>
+      </c>
+      <c r="I126">
+        <v>33.479792000000003</v>
+      </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
@@ -4674,9 +5423,18 @@
       <c r="E127">
         <v>1</v>
       </c>
-      <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
-      <c r="I127" s="3"/>
+      <c r="F127" s="3">
+        <v>91384260439.270004</v>
+      </c>
+      <c r="G127">
+        <v>4.5400969999999994</v>
+      </c>
+      <c r="H127">
+        <v>33.516843999999999</v>
+      </c>
+      <c r="I127">
+        <v>33.515726000000001</v>
+      </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
@@ -4694,9 +5452,18 @@
       <c r="E128">
         <v>1</v>
       </c>
-      <c r="G128" s="3"/>
-      <c r="H128" s="3"/>
-      <c r="I128" s="3"/>
+      <c r="F128" s="3">
+        <v>103058344258.09999</v>
+      </c>
+      <c r="G128">
+        <v>4.5448190000000004</v>
+      </c>
+      <c r="H128">
+        <v>33.550967999999997</v>
+      </c>
+      <c r="I128">
+        <v>33.549849000000002</v>
+      </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
@@ -4714,9 +5481,18 @@
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
-      <c r="I129" s="3"/>
+      <c r="F129" s="3">
+        <v>86254935513.25</v>
+      </c>
+      <c r="G129">
+        <v>4.5495929999999998</v>
+      </c>
+      <c r="H129">
+        <v>33.585473</v>
+      </c>
+      <c r="I129">
+        <v>33.584353</v>
+      </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
@@ -4734,9 +5510,18 @@
       <c r="E130">
         <v>1</v>
       </c>
-      <c r="G130" s="3"/>
-      <c r="H130" s="3"/>
-      <c r="I130" s="3"/>
+      <c r="F130" s="3">
+        <v>86254935513.25</v>
+      </c>
+      <c r="G130">
+        <v>4.5639329999999996</v>
+      </c>
+      <c r="H130">
+        <v>33.689115999999999</v>
+      </c>
+      <c r="I130">
+        <v>33.687992000000001</v>
+      </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
@@ -4754,9 +5539,18 @@
       <c r="E131">
         <v>1</v>
       </c>
-      <c r="G131" s="3"/>
-      <c r="H131" s="3"/>
-      <c r="I131" s="3"/>
+      <c r="F131" s="3">
+        <v>89055896771.649994</v>
+      </c>
+      <c r="G131">
+        <v>4.5687090000000001</v>
+      </c>
+      <c r="H131">
+        <v>33.723633999999997</v>
+      </c>
+      <c r="I131">
+        <v>33.722508000000005</v>
+      </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
@@ -4774,9 +5568,18 @@
       <c r="E132">
         <v>1</v>
       </c>
-      <c r="G132" s="3"/>
-      <c r="H132" s="3"/>
-      <c r="I132" s="3"/>
+      <c r="F132" s="3">
+        <v>90706203050.570007</v>
+      </c>
+      <c r="G132">
+        <v>4.5735089999999996</v>
+      </c>
+      <c r="H132">
+        <v>33.758321000000002</v>
+      </c>
+      <c r="I132">
+        <v>33.757193000000001</v>
+      </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
@@ -4794,9 +5597,18 @@
       <c r="E133">
         <v>1</v>
       </c>
-      <c r="G133" s="3"/>
-      <c r="H133" s="3"/>
-      <c r="I133" s="3"/>
+      <c r="F133" s="3">
+        <v>90706203050.570007</v>
+      </c>
+      <c r="G133">
+        <v>4.5782600000000002</v>
+      </c>
+      <c r="H133">
+        <v>33.792650999999999</v>
+      </c>
+      <c r="I133">
+        <v>33.791521000000003</v>
+      </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
@@ -4814,9 +5626,18 @@
       <c r="E134">
         <v>1</v>
       </c>
-      <c r="G134" s="3"/>
-      <c r="H134" s="3"/>
-      <c r="I134" s="3"/>
+      <c r="F134" s="3">
+        <v>90706203050.570007</v>
+      </c>
+      <c r="G134">
+        <v>4.5830029999999997</v>
+      </c>
+      <c r="H134">
+        <v>33.826919000000004</v>
+      </c>
+      <c r="I134">
+        <v>33.825786999999998</v>
+      </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
@@ -4834,9 +5655,18 @@
       <c r="E135">
         <v>1</v>
       </c>
-      <c r="G135" s="3"/>
-      <c r="H135" s="3"/>
-      <c r="I135" s="3"/>
+      <c r="F135" s="3">
+        <v>83633731263.300003</v>
+      </c>
+      <c r="G135">
+        <v>4.5971299999999999</v>
+      </c>
+      <c r="H135">
+        <v>33.928953999999997</v>
+      </c>
+      <c r="I135">
+        <v>33.927818000000002</v>
+      </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
@@ -4854,9 +5684,18 @@
       <c r="E136">
         <v>1</v>
       </c>
-      <c r="G136" s="3"/>
-      <c r="H136" s="3"/>
-      <c r="I136" s="3"/>
+      <c r="F136" s="3">
+        <v>87221853328.360001</v>
+      </c>
+      <c r="G136">
+        <v>4.6019219999999992</v>
+      </c>
+      <c r="H136">
+        <v>33.963577000000001</v>
+      </c>
+      <c r="I136">
+        <v>33.962440000000001</v>
+      </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
@@ -4874,9 +5713,18 @@
       <c r="E137">
         <v>1</v>
       </c>
-      <c r="G137" s="3"/>
-      <c r="H137" s="3"/>
-      <c r="I137" s="3"/>
+      <c r="F137" s="3">
+        <v>91722829021.339996</v>
+      </c>
+      <c r="G137">
+        <v>4.6068599999999993</v>
+      </c>
+      <c r="H137">
+        <v>33.999275000000004</v>
+      </c>
+      <c r="I137">
+        <v>33.998137999999997</v>
+      </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
@@ -4894,9 +5742,18 @@
       <c r="E138">
         <v>1</v>
       </c>
-      <c r="G138" s="3"/>
-      <c r="H138" s="3"/>
-      <c r="I138" s="3"/>
+      <c r="F138" s="3">
+        <v>90478684984.479996</v>
+      </c>
+      <c r="G138">
+        <v>4.6107110000000002</v>
+      </c>
+      <c r="H138">
+        <v>34.026951000000004</v>
+      </c>
+      <c r="I138">
+        <v>34.025813999999997</v>
+      </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
@@ -4914,9 +5771,18 @@
       <c r="E139">
         <v>1</v>
       </c>
-      <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
-      <c r="I139" s="3"/>
+      <c r="F139" s="3">
+        <v>92651690782.73999</v>
+      </c>
+      <c r="G139">
+        <v>4.6145800000000001</v>
+      </c>
+      <c r="H139">
+        <v>34.054756000000005</v>
+      </c>
+      <c r="I139">
+        <v>34.053618999999998</v>
+      </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
@@ -4934,9 +5800,18 @@
       <c r="E140">
         <v>1</v>
       </c>
-      <c r="G140" s="3"/>
-      <c r="H140" s="3"/>
-      <c r="I140" s="3"/>
+      <c r="F140" s="3">
+        <v>92651690782.73999</v>
+      </c>
+      <c r="G140">
+        <v>4.626131</v>
+      </c>
+      <c r="H140">
+        <v>34.137751999999999</v>
+      </c>
+      <c r="I140">
+        <v>34.136614999999999</v>
+      </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
@@ -4954,9 +5829,18 @@
       <c r="E141">
         <v>1</v>
       </c>
-      <c r="G141" s="3"/>
-      <c r="H141" s="3"/>
-      <c r="I141" s="3"/>
+      <c r="F141" s="3">
+        <v>92651690782.73999</v>
+      </c>
+      <c r="G141">
+        <v>4.6299979999999996</v>
+      </c>
+      <c r="H141">
+        <v>34.165535000000006</v>
+      </c>
+      <c r="I141">
+        <v>34.164397999999998</v>
+      </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
@@ -4974,9 +5858,18 @@
       <c r="E142">
         <v>1</v>
       </c>
-      <c r="G142" s="3"/>
-      <c r="H142" s="3"/>
-      <c r="I142" s="3"/>
+      <c r="F142" s="3">
+        <v>90656455007.75</v>
+      </c>
+      <c r="G142">
+        <v>4.6336279999999999</v>
+      </c>
+      <c r="H142">
+        <v>34.191569000000001</v>
+      </c>
+      <c r="I142">
+        <v>34.190430999999997</v>
+      </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
@@ -4994,9 +5887,18 @@
       <c r="E143">
         <v>1</v>
       </c>
-      <c r="G143" s="3"/>
-      <c r="H143" s="3"/>
-      <c r="I143" s="3"/>
+      <c r="F143" s="3">
+        <v>90308589521.720001</v>
+      </c>
+      <c r="G143">
+        <v>4.6372520000000002</v>
+      </c>
+      <c r="H143">
+        <v>34.217563999999996</v>
+      </c>
+      <c r="I143">
+        <v>34.216425000000001</v>
+      </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
@@ -5014,9 +5916,18 @@
       <c r="E144">
         <v>1</v>
       </c>
-      <c r="G144" s="3"/>
-      <c r="H144" s="3"/>
-      <c r="I144" s="3"/>
+      <c r="F144" s="3">
+        <v>110437642115.51001</v>
+      </c>
+      <c r="G144">
+        <v>4.6409210000000005</v>
+      </c>
+      <c r="H144">
+        <v>34.24389</v>
+      </c>
+      <c r="I144">
+        <v>34.242750000000001</v>
+      </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
@@ -5034,9 +5945,18 @@
       <c r="E145">
         <v>1</v>
       </c>
-      <c r="G145" s="3"/>
-      <c r="H145" s="3"/>
-      <c r="I145" s="3"/>
+      <c r="F145" s="3">
+        <v>94431599086.240005</v>
+      </c>
+      <c r="G145">
+        <v>4.6521499999999998</v>
+      </c>
+      <c r="H145">
+        <v>34.324485000000003</v>
+      </c>
+      <c r="I145">
+        <v>34.323340999999999</v>
+      </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
@@ -5054,9 +5974,18 @@
       <c r="E146">
         <v>1</v>
       </c>
-      <c r="G146" s="3"/>
-      <c r="H146" s="3"/>
-      <c r="I146" s="3"/>
+      <c r="F146" s="3">
+        <v>104782205542.78</v>
+      </c>
+      <c r="G146">
+        <v>4.6562510000000001</v>
+      </c>
+      <c r="H146">
+        <v>34.353988999999999</v>
+      </c>
+      <c r="I146">
+        <v>34.352839000000003</v>
+      </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
@@ -5074,9 +6003,18 @@
       <c r="E147">
         <v>1</v>
       </c>
-      <c r="G147" s="3"/>
-      <c r="H147" s="3"/>
-      <c r="I147" s="3"/>
+      <c r="F147" s="3">
+        <v>104782205542.78</v>
+      </c>
+      <c r="G147">
+        <v>4.6610139999999998</v>
+      </c>
+      <c r="H147">
+        <v>34.388375000000003</v>
+      </c>
+      <c r="I147">
+        <v>34.387222999999999</v>
+      </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
@@ -5094,9 +6032,18 @@
       <c r="E148">
         <v>1</v>
       </c>
-      <c r="G148" s="3"/>
-      <c r="H148" s="3"/>
-      <c r="I148" s="3"/>
+      <c r="F148" s="3">
+        <v>104782205542.78</v>
+      </c>
+      <c r="G148">
+        <v>4.6662319999999999</v>
+      </c>
+      <c r="H148">
+        <v>34.426116</v>
+      </c>
+      <c r="I148">
+        <v>34.424957999999997</v>
+      </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
@@ -5114,9 +6061,18 @@
       <c r="E149">
         <v>1</v>
       </c>
-      <c r="G149" s="3"/>
-      <c r="H149" s="3"/>
-      <c r="I149" s="3"/>
+      <c r="F149" s="3">
+        <v>100103958107.73001</v>
+      </c>
+      <c r="G149">
+        <v>4.6889149999999997</v>
+      </c>
+      <c r="H149">
+        <v>34.590426000000001</v>
+      </c>
+      <c r="I149">
+        <v>34.589245999999996</v>
+      </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
@@ -5134,9 +6090,18 @@
       <c r="E150">
         <v>1</v>
       </c>
-      <c r="G150" s="3"/>
-      <c r="H150" s="3"/>
-      <c r="I150" s="3"/>
+      <c r="F150" s="3">
+        <v>109045122307.35001</v>
+      </c>
+      <c r="G150">
+        <v>4.6951609999999997</v>
+      </c>
+      <c r="H150">
+        <v>34.635739000000001</v>
+      </c>
+      <c r="I150">
+        <v>34.634553999999994</v>
+      </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
@@ -5154,9 +6119,18 @@
       <c r="E151">
         <v>1</v>
       </c>
-      <c r="G151" s="3"/>
-      <c r="H151" s="3"/>
-      <c r="I151" s="3"/>
+      <c r="F151" s="3">
+        <v>113743942454.55</v>
+      </c>
+      <c r="G151">
+        <v>4.7024840000000001</v>
+      </c>
+      <c r="H151">
+        <v>34.688997999999998</v>
+      </c>
+      <c r="I151">
+        <v>34.687806999999999</v>
+      </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
@@ -5174,9 +6148,18 @@
       <c r="E152">
         <v>1</v>
       </c>
-      <c r="G152" s="3"/>
-      <c r="H152" s="3"/>
-      <c r="I152" s="3"/>
+      <c r="F152" s="3">
+        <v>120429142313.69</v>
+      </c>
+      <c r="G152">
+        <v>4.7100580000000001</v>
+      </c>
+      <c r="H152">
+        <v>34.744107000000007</v>
+      </c>
+      <c r="I152">
+        <v>34.742910000000002</v>
+      </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
@@ -5194,9 +6177,18 @@
       <c r="E153">
         <v>1</v>
       </c>
-      <c r="G153" s="3"/>
-      <c r="H153" s="3"/>
-      <c r="I153" s="3"/>
+      <c r="F153" s="3">
+        <v>128135859716.42999</v>
+      </c>
+      <c r="G153">
+        <v>4.7164470000000005</v>
+      </c>
+      <c r="H153">
+        <v>34.790472000000001</v>
+      </c>
+      <c r="I153">
+        <v>34.789270999999999</v>
+      </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
@@ -5214,9 +6206,18 @@
       <c r="E154">
         <v>1</v>
       </c>
-      <c r="G154" s="3"/>
-      <c r="H154" s="3"/>
-      <c r="I154" s="3"/>
+      <c r="F154" s="3">
+        <v>128135859716.42999</v>
+      </c>
+      <c r="G154">
+        <v>4.7295929999999995</v>
+      </c>
+      <c r="H154">
+        <v>34.885150000000003</v>
+      </c>
+      <c r="I154">
+        <v>34.883935000000001</v>
+      </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
@@ -5234,9 +6235,18 @@
       <c r="E155">
         <v>1</v>
       </c>
-      <c r="G155" s="3"/>
-      <c r="H155" s="3"/>
-      <c r="I155" s="3"/>
+      <c r="F155" s="3">
+        <v>128135859716.42999</v>
+      </c>
+      <c r="G155">
+        <v>4.7336459999999994</v>
+      </c>
+      <c r="H155">
+        <v>34.914279000000001</v>
+      </c>
+      <c r="I155">
+        <v>34.913063000000001</v>
+      </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
@@ -5254,9 +6264,18 @@
       <c r="E156">
         <v>1</v>
       </c>
-      <c r="G156" s="3"/>
-      <c r="H156" s="3"/>
-      <c r="I156" s="3"/>
+      <c r="F156" s="3">
+        <v>125408459198.37001</v>
+      </c>
+      <c r="G156">
+        <v>4.7373519999999996</v>
+      </c>
+      <c r="H156">
+        <v>34.940843000000001</v>
+      </c>
+      <c r="I156">
+        <v>34.939627000000002</v>
+      </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
@@ -5274,9 +6293,18 @@
       <c r="E157">
         <v>1</v>
       </c>
-      <c r="G157" s="3"/>
-      <c r="H157" s="3"/>
-      <c r="I157" s="3"/>
+      <c r="F157" s="3">
+        <v>138467186613.01999</v>
+      </c>
+      <c r="G157">
+        <v>4.7412619999999999</v>
+      </c>
+      <c r="H157">
+        <v>34.968910000000001</v>
+      </c>
+      <c r="I157">
+        <v>34.967689</v>
+      </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
@@ -5294,9 +6322,18 @@
       <c r="E158">
         <v>1</v>
       </c>
-      <c r="G158" s="3"/>
-      <c r="H158" s="3"/>
-      <c r="I158" s="3"/>
+      <c r="F158" s="3">
+        <v>124725412220.07999</v>
+      </c>
+      <c r="G158">
+        <v>4.7456389999999997</v>
+      </c>
+      <c r="H158">
+        <v>35.000421000000003</v>
+      </c>
+      <c r="I158">
+        <v>34.999195</v>
+      </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
@@ -5314,9 +6351,18 @@
       <c r="E159">
         <v>1</v>
       </c>
-      <c r="G159" s="3"/>
-      <c r="H159" s="3"/>
-      <c r="I159" s="3"/>
+      <c r="F159" s="3">
+        <v>116357975050.97</v>
+      </c>
+      <c r="G159">
+        <v>4.7623800000000003</v>
+      </c>
+      <c r="H159">
+        <v>35.121576999999995</v>
+      </c>
+      <c r="I159">
+        <v>35.120339999999999</v>
+      </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
@@ -5334,9 +6380,18 @@
       <c r="E160">
         <v>1</v>
       </c>
-      <c r="G160" s="3"/>
-      <c r="H160" s="3"/>
-      <c r="I160" s="3"/>
+      <c r="F160" s="3">
+        <v>112747521646.28</v>
+      </c>
+      <c r="G160">
+        <v>4.7690440000000001</v>
+      </c>
+      <c r="H160">
+        <v>35.169947999999998</v>
+      </c>
+      <c r="I160">
+        <v>35.168705000000003</v>
+      </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
@@ -5354,9 +6409,18 @@
       <c r="E161">
         <v>1</v>
       </c>
-      <c r="G161" s="3"/>
-      <c r="H161" s="3"/>
-      <c r="I161" s="3"/>
+      <c r="F161" s="3">
+        <v>112747521646.28</v>
+      </c>
+      <c r="G161">
+        <v>4.7752420000000004</v>
+      </c>
+      <c r="H161">
+        <v>35.214883</v>
+      </c>
+      <c r="I161">
+        <v>35.213637999999996</v>
+      </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
@@ -5374,9 +6438,18 @@
       <c r="E162">
         <v>1</v>
       </c>
-      <c r="G162" s="3"/>
-      <c r="H162" s="3"/>
-      <c r="I162" s="3"/>
+      <c r="F162" s="3">
+        <v>112747521646.28</v>
+      </c>
+      <c r="G162">
+        <v>4.7793950000000001</v>
+      </c>
+      <c r="H162">
+        <v>35.244737000000001</v>
+      </c>
+      <c r="I162">
+        <v>35.243489000000004</v>
+      </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
@@ -5394,9 +6467,18 @@
       <c r="E163">
         <v>1</v>
       </c>
-      <c r="G163" s="3"/>
-      <c r="H163" s="3"/>
-      <c r="I163" s="3"/>
+      <c r="F163" s="3">
+        <v>108223878241.19</v>
+      </c>
+      <c r="G163">
+        <v>4.7833579999999998</v>
+      </c>
+      <c r="H163">
+        <v>35.273184999999998</v>
+      </c>
+      <c r="I163">
+        <v>35.271934000000002</v>
+      </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
@@ -5414,9 +6496,18 @@
       <c r="E164">
         <v>1</v>
       </c>
-      <c r="G164" s="3"/>
-      <c r="H164" s="3"/>
-      <c r="I164" s="3"/>
+      <c r="F164" s="3">
+        <v>99974100397.220001</v>
+      </c>
+      <c r="G164">
+        <v>4.7939089999999993</v>
+      </c>
+      <c r="H164">
+        <v>35.348665999999994</v>
+      </c>
+      <c r="I164">
+        <v>35.347411999999998</v>
+      </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
@@ -5434,9 +6525,18 @@
       <c r="E165">
         <v>1</v>
       </c>
-      <c r="G165" s="3"/>
-      <c r="H165" s="3"/>
-      <c r="I165" s="3"/>
+      <c r="F165" s="3">
+        <v>92343464401.170013</v>
+      </c>
+      <c r="G165">
+        <v>4.7972999999999999</v>
+      </c>
+      <c r="H165">
+        <v>35.372895999999997</v>
+      </c>
+      <c r="I165">
+        <v>35.371641000000004</v>
+      </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
@@ -5454,9 +6554,18 @@
       <c r="E166">
         <v>1</v>
       </c>
-      <c r="G166" s="3"/>
-      <c r="H166" s="3"/>
-      <c r="I166" s="3"/>
+      <c r="F166" s="3">
+        <v>71029084250.100006</v>
+      </c>
+      <c r="G166">
+        <v>4.800751</v>
+      </c>
+      <c r="H166">
+        <v>35.397562000000001</v>
+      </c>
+      <c r="I166">
+        <v>35.396305999999996</v>
+      </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
@@ -5474,9 +6583,18 @@
       <c r="E167">
         <v>1</v>
       </c>
-      <c r="G167" s="3"/>
-      <c r="H167" s="3"/>
-      <c r="I167" s="3"/>
+      <c r="F167" s="3">
+        <v>71029084250.100006</v>
+      </c>
+      <c r="G167">
+        <v>4.8068850000000003</v>
+      </c>
+      <c r="H167">
+        <v>35.441232999999997</v>
+      </c>
+      <c r="I167">
+        <v>35.439976000000001</v>
+      </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
@@ -5494,9 +6612,18 @@
       <c r="E168">
         <v>1</v>
       </c>
-      <c r="G168" s="3"/>
-      <c r="H168" s="3"/>
-      <c r="I168" s="3"/>
+      <c r="F168" s="3">
+        <v>71029084250.100006</v>
+      </c>
+      <c r="G168">
+        <v>4.8163100000000005</v>
+      </c>
+      <c r="H168">
+        <v>35.508389000000001</v>
+      </c>
+      <c r="I168">
+        <v>35.507131000000001</v>
+      </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
@@ -5514,9 +6641,18 @@
       <c r="E169">
         <v>1</v>
       </c>
-      <c r="G169" s="3"/>
-      <c r="H169" s="3"/>
-      <c r="I169" s="3"/>
+      <c r="F169" s="3">
+        <v>71029084250.100006</v>
+      </c>
+      <c r="G169">
+        <v>4.8195060000000005</v>
+      </c>
+      <c r="H169">
+        <v>35.531169999999996</v>
+      </c>
+      <c r="I169">
+        <v>35.529911999999996</v>
+      </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
@@ -5534,9 +6670,18 @@
       <c r="E170">
         <v>1</v>
       </c>
-      <c r="G170" s="3"/>
-      <c r="H170" s="3"/>
-      <c r="I170" s="3"/>
+      <c r="F170" s="3">
+        <v>85181502546.880005</v>
+      </c>
+      <c r="G170">
+        <v>4.8226450000000005</v>
+      </c>
+      <c r="H170">
+        <v>35.553529000000005</v>
+      </c>
+      <c r="I170">
+        <v>35.552270999999998</v>
+      </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
@@ -5554,9 +6699,18 @@
       <c r="E171">
         <v>1</v>
       </c>
-      <c r="G171" s="3"/>
-      <c r="H171" s="3"/>
-      <c r="I171" s="3"/>
+      <c r="F171" s="3">
+        <v>97735653973.860001</v>
+      </c>
+      <c r="G171">
+        <v>4.8257560000000002</v>
+      </c>
+      <c r="H171">
+        <v>35.575685</v>
+      </c>
+      <c r="I171">
+        <v>35.574427</v>
+      </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
@@ -5574,9 +6728,18 @@
       <c r="E172">
         <v>1</v>
       </c>
-      <c r="G172" s="3"/>
-      <c r="H172" s="3"/>
-      <c r="I172" s="3"/>
+      <c r="F172" s="3">
+        <v>78915928018.279999</v>
+      </c>
+      <c r="G172">
+        <v>4.8287659999999999</v>
+      </c>
+      <c r="H172">
+        <v>35.597093000000001</v>
+      </c>
+      <c r="I172">
+        <v>35.595835000000001</v>
+      </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
@@ -5594,9 +6757,18 @@
       <c r="E173">
         <v>1</v>
       </c>
-      <c r="G173" s="3"/>
-      <c r="H173" s="3"/>
-      <c r="I173" s="3"/>
+      <c r="F173" s="3">
+        <v>80818916126.619995</v>
+      </c>
+      <c r="G173">
+        <v>4.8377619999999997</v>
+      </c>
+      <c r="H173">
+        <v>35.661059999999999</v>
+      </c>
+      <c r="I173">
+        <v>35.659802000000006</v>
+      </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
@@ -5614,9 +6786,18 @@
       <c r="E174">
         <v>1</v>
       </c>
-      <c r="G174" s="3"/>
-      <c r="H174" s="3"/>
-      <c r="I174" s="3"/>
+      <c r="F174" s="3">
+        <v>73609391748.649994</v>
+      </c>
+      <c r="G174">
+        <v>4.840579</v>
+      </c>
+      <c r="H174">
+        <v>35.681044999999997</v>
+      </c>
+      <c r="I174">
+        <v>35.679786999999997</v>
+      </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
@@ -5634,9 +6815,18 @@
       <c r="E175">
         <v>1</v>
       </c>
-      <c r="G175" s="3"/>
-      <c r="H175" s="3"/>
-      <c r="I175" s="3"/>
+      <c r="F175" s="3">
+        <v>73609391748.649994</v>
+      </c>
+      <c r="G175">
+        <v>4.8432700000000004</v>
+      </c>
+      <c r="H175">
+        <v>35.700099999999999</v>
+      </c>
+      <c r="I175">
+        <v>35.698841999999999</v>
+      </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
@@ -5654,9 +6844,18 @@
       <c r="E176">
         <v>1</v>
       </c>
-      <c r="G176" s="3"/>
-      <c r="H176" s="3"/>
-      <c r="I176" s="3"/>
+      <c r="F176" s="3">
+        <v>73609391748.649994</v>
+      </c>
+      <c r="G176">
+        <v>4.8461270000000001</v>
+      </c>
+      <c r="H176">
+        <v>35.720379000000001</v>
+      </c>
+      <c r="I176">
+        <v>35.719120000000004</v>
+      </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
@@ -5674,9 +6873,18 @@
       <c r="E177">
         <v>1</v>
       </c>
-      <c r="G177" s="3"/>
-      <c r="H177" s="3"/>
-      <c r="I177" s="3"/>
+      <c r="F177" s="3">
+        <v>91624704580.919998</v>
+      </c>
+      <c r="G177">
+        <v>4.8593919999999997</v>
+      </c>
+      <c r="H177">
+        <v>35.814219999999999</v>
+      </c>
+      <c r="I177">
+        <v>35.812961000000001</v>
+      </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
@@ -5694,9 +6902,18 @@
       <c r="E178">
         <v>1</v>
       </c>
-      <c r="G178" s="3"/>
-      <c r="H178" s="3"/>
-      <c r="I178" s="3"/>
+      <c r="F178" s="3">
+        <v>91118697119.009995</v>
+      </c>
+      <c r="G178">
+        <v>4.862006</v>
+      </c>
+      <c r="H178">
+        <v>35.832695000000001</v>
+      </c>
+      <c r="I178">
+        <v>35.831436000000004</v>
+      </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
@@ -5714,9 +6931,18 @@
       <c r="E179">
         <v>1</v>
       </c>
-      <c r="G179" s="3"/>
-      <c r="H179" s="3"/>
-      <c r="I179" s="3"/>
+      <c r="F179" s="3">
+        <v>83798006883.300003</v>
+      </c>
+      <c r="G179">
+        <v>4.8647160000000005</v>
+      </c>
+      <c r="H179">
+        <v>35.851877999999999</v>
+      </c>
+      <c r="I179">
+        <v>35.850611999999998</v>
+      </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
@@ -5734,9 +6960,18 @@
       <c r="E180">
         <v>1</v>
       </c>
-      <c r="G180" s="3"/>
-      <c r="H180" s="3"/>
-      <c r="I180" s="3"/>
+      <c r="F180" s="3">
+        <v>80243705626.309998</v>
+      </c>
+      <c r="G180">
+        <v>4.867489</v>
+      </c>
+      <c r="H180">
+        <v>35.871524000000001</v>
+      </c>
+      <c r="I180">
+        <v>35.870250999999996</v>
+      </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
@@ -5754,9 +6989,18 @@
       <c r="E181">
         <v>1</v>
       </c>
-      <c r="G181" s="3"/>
-      <c r="H181" s="3"/>
-      <c r="I181" s="3"/>
+      <c r="F181" s="3">
+        <v>67359340478.049995</v>
+      </c>
+      <c r="G181">
+        <v>4.8751369999999996</v>
+      </c>
+      <c r="H181">
+        <v>35.925521000000003</v>
+      </c>
+      <c r="I181">
+        <v>35.924233000000001</v>
+      </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
@@ -5774,9 +7018,18 @@
       <c r="E182">
         <v>1</v>
       </c>
-      <c r="G182" s="3"/>
-      <c r="H182" s="3"/>
-      <c r="I182" s="3"/>
+      <c r="F182" s="3">
+        <v>67359340478.049995</v>
+      </c>
+      <c r="G182">
+        <v>4.877599</v>
+      </c>
+      <c r="H182">
+        <v>35.942870999999997</v>
+      </c>
+      <c r="I182">
+        <v>35.941578</v>
+      </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
@@ -5794,9 +7047,18 @@
       <c r="E183">
         <v>1</v>
       </c>
-      <c r="G183" s="3"/>
-      <c r="H183" s="3"/>
-      <c r="I183" s="3"/>
+      <c r="F183" s="3">
+        <v>67359340478.049995</v>
+      </c>
+      <c r="G183">
+        <v>4.8800789999999994</v>
+      </c>
+      <c r="H183">
+        <v>35.960358999999997</v>
+      </c>
+      <c r="I183">
+        <v>35.959061999999996</v>
+      </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
@@ -5814,9 +7076,18 @@
       <c r="E184">
         <v>1</v>
       </c>
-      <c r="G184" s="3"/>
-      <c r="H184" s="3"/>
-      <c r="I184" s="3"/>
+      <c r="F184" s="3">
+        <v>61980202257.270004</v>
+      </c>
+      <c r="G184">
+        <v>4.8825529999999997</v>
+      </c>
+      <c r="H184">
+        <v>35.977798</v>
+      </c>
+      <c r="I184">
+        <v>35.976495999999997</v>
+      </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
@@ -5834,9 +7105,18 @@
       <c r="E185">
         <v>1</v>
       </c>
-      <c r="G185" s="3"/>
-      <c r="H185" s="3"/>
-      <c r="I185" s="3"/>
+      <c r="F185" s="3">
+        <v>77932950398.470001</v>
+      </c>
+      <c r="G185">
+        <v>4.8851069999999996</v>
+      </c>
+      <c r="H185">
+        <v>35.995829000000001</v>
+      </c>
+      <c r="I185">
+        <v>35.994523000000001</v>
+      </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
@@ -5854,9 +7134,18 @@
       <c r="E186">
         <v>1</v>
       </c>
-      <c r="G186" s="3"/>
-      <c r="H186" s="3"/>
-      <c r="I186" s="3"/>
+      <c r="F186" s="3">
+        <v>87776969992.100006</v>
+      </c>
+      <c r="G186">
+        <v>4.8947770000000004</v>
+      </c>
+      <c r="H186">
+        <v>36.063915999999999</v>
+      </c>
+      <c r="I186">
+        <v>36.062589999999993</v>
+      </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
@@ -5874,9 +7163,18 @@
       <c r="E187">
         <v>1</v>
       </c>
-      <c r="G187" s="3"/>
-      <c r="H187" s="3"/>
-      <c r="I187" s="3"/>
+      <c r="F187" s="3">
+        <v>90972264635.020004</v>
+      </c>
+      <c r="G187">
+        <v>4.8973880000000003</v>
+      </c>
+      <c r="H187">
+        <v>36.082358999999997</v>
+      </c>
+      <c r="I187">
+        <v>36.081021</v>
+      </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
@@ -5894,9 +7192,18 @@
       <c r="E188">
         <v>1</v>
       </c>
-      <c r="G188" s="3"/>
-      <c r="H188" s="3"/>
-      <c r="I188" s="3"/>
+      <c r="F188" s="3">
+        <v>89994257858.470001</v>
+      </c>
+      <c r="G188">
+        <v>4.8996189999999995</v>
+      </c>
+      <c r="H188">
+        <v>36.098005000000001</v>
+      </c>
+      <c r="I188">
+        <v>36.096650000000004</v>
+      </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
@@ -5914,9 +7221,18 @@
       <c r="E189">
         <v>1</v>
       </c>
-      <c r="G189" s="3"/>
-      <c r="H189" s="3"/>
-      <c r="I189" s="3"/>
+      <c r="F189" s="3">
+        <v>89994257858.470001</v>
+      </c>
+      <c r="G189">
+        <v>4.9018350000000002</v>
+      </c>
+      <c r="H189">
+        <v>36.113537999999998</v>
+      </c>
+      <c r="I189">
+        <v>36.112164999999997</v>
+      </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
@@ -5934,9 +7250,18 @@
       <c r="E190">
         <v>1</v>
       </c>
-      <c r="G190" s="3"/>
-      <c r="H190" s="3"/>
-      <c r="I190" s="3"/>
+      <c r="F190" s="3">
+        <v>89994257858.470001</v>
+      </c>
+      <c r="G190">
+        <v>4.9082319999999999</v>
+      </c>
+      <c r="H190">
+        <v>36.158285000000006</v>
+      </c>
+      <c r="I190">
+        <v>36.156841999999997</v>
+      </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
@@ -5954,9 +7279,18 @@
       <c r="E191">
         <v>1</v>
       </c>
-      <c r="G191" s="3"/>
-      <c r="H191" s="3"/>
-      <c r="I191" s="3"/>
+      <c r="F191" s="3">
+        <v>88391043725.809998</v>
+      </c>
+      <c r="G191">
+        <v>4.9105100000000004</v>
+      </c>
+      <c r="H191">
+        <v>36.174269000000002</v>
+      </c>
+      <c r="I191">
+        <v>36.172803000000002</v>
+      </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
@@ -5974,9 +7308,18 @@
       <c r="E192">
         <v>1</v>
       </c>
-      <c r="G192" s="3"/>
-      <c r="H192" s="3"/>
-      <c r="I192" s="3"/>
+      <c r="F192" s="3">
+        <v>94060283205.600006</v>
+      </c>
+      <c r="G192">
+        <v>4.9126329999999996</v>
+      </c>
+      <c r="H192">
+        <v>36.189118000000001</v>
+      </c>
+      <c r="I192">
+        <v>36.187626999999999</v>
+      </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
@@ -5994,9 +7337,18 @@
       <c r="E193">
         <v>1</v>
       </c>
-      <c r="G193" s="3"/>
-      <c r="H193" s="3"/>
-      <c r="I193" s="3"/>
+      <c r="F193" s="3">
+        <v>103158419081.07001</v>
+      </c>
+      <c r="G193">
+        <v>4.9147990000000004</v>
+      </c>
+      <c r="H193">
+        <v>36.204277000000005</v>
+      </c>
+      <c r="I193">
+        <v>36.202764999999999</v>
+      </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
@@ -6014,9 +7366,18 @@
       <c r="E194">
         <v>1</v>
       </c>
-      <c r="G194" s="3"/>
-      <c r="H194" s="3"/>
-      <c r="I194" s="3"/>
+      <c r="F194" s="3">
+        <v>98636181972.990005</v>
+      </c>
+      <c r="G194">
+        <v>4.9169549999999997</v>
+      </c>
+      <c r="H194">
+        <v>36.219364999999996</v>
+      </c>
+      <c r="I194">
+        <v>36.217828000000004</v>
+      </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
@@ -6034,9 +7395,18 @@
       <c r="E195">
         <v>1</v>
       </c>
-      <c r="G195" s="3"/>
-      <c r="H195" s="3"/>
-      <c r="I195" s="3"/>
+      <c r="F195" s="3">
+        <v>100548029433.72</v>
+      </c>
+      <c r="G195">
+        <v>4.923603</v>
+      </c>
+      <c r="H195">
+        <v>36.265946000000007</v>
+      </c>
+      <c r="I195">
+        <v>36.264334000000005</v>
+      </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
@@ -6054,9 +7424,18 @@
       <c r="E196">
         <v>1</v>
       </c>
-      <c r="G196" s="3"/>
-      <c r="H196" s="3"/>
-      <c r="I196" s="3"/>
+      <c r="F196" s="3">
+        <v>100548029433.72</v>
+      </c>
+      <c r="G196">
+        <v>4.9258220000000001</v>
+      </c>
+      <c r="H196">
+        <v>36.281491000000003</v>
+      </c>
+      <c r="I196">
+        <v>36.279855000000005</v>
+      </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
@@ -6074,9 +7453,18 @@
       <c r="E197">
         <v>1</v>
       </c>
-      <c r="G197" s="3"/>
-      <c r="H197" s="3"/>
-      <c r="I197" s="3"/>
+      <c r="F197" s="3">
+        <v>100548029433.72</v>
+      </c>
+      <c r="G197">
+        <v>4.9334440000000006</v>
+      </c>
+      <c r="H197">
+        <v>36.335235999999995</v>
+      </c>
+      <c r="I197">
+        <v>36.333535000000005</v>
+      </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
@@ -6094,9 +7482,18 @@
       <c r="E198">
         <v>1</v>
       </c>
-      <c r="G198" s="3"/>
-      <c r="H198" s="3"/>
-      <c r="I198" s="3"/>
+      <c r="F198" s="3">
+        <v>99097402966.940002</v>
+      </c>
+      <c r="G198">
+        <v>4.9416260000000003</v>
+      </c>
+      <c r="H198">
+        <v>36.393091999999996</v>
+      </c>
+      <c r="I198">
+        <v>36.391331000000001</v>
+      </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
@@ -6114,9 +7511,18 @@
       <c r="E199">
         <v>1</v>
       </c>
-      <c r="G199" s="3"/>
-      <c r="H199" s="3"/>
-      <c r="I199" s="3"/>
+      <c r="F199" s="3">
+        <v>108698899719.83</v>
+      </c>
+      <c r="G199">
+        <v>4.9444359999999996</v>
+      </c>
+      <c r="H199">
+        <v>36.412990000000001</v>
+      </c>
+      <c r="I199">
+        <v>36.411200999999998</v>
+      </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
@@ -6134,9 +7540,18 @@
       <c r="E200">
         <v>1</v>
       </c>
-      <c r="G200" s="3"/>
-      <c r="H200" s="3"/>
-      <c r="I200" s="3"/>
+      <c r="F200" s="3">
+        <v>97824642562.600006</v>
+      </c>
+      <c r="G200">
+        <v>4.9573689999999999</v>
+      </c>
+      <c r="H200">
+        <v>36.505831000000001</v>
+      </c>
+      <c r="I200">
+        <v>36.504036999999997</v>
+      </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
@@ -6154,9 +7569,18 @@
       <c r="E201">
         <v>1</v>
       </c>
-      <c r="G201" s="3"/>
-      <c r="H201" s="3"/>
-      <c r="I201" s="3"/>
+      <c r="F201" s="3">
+        <v>99885633692.899994</v>
+      </c>
+      <c r="G201">
+        <v>4.9678570000000004</v>
+      </c>
+      <c r="H201">
+        <v>36.580657000000002</v>
+      </c>
+      <c r="I201">
+        <v>36.578858999999994</v>
+      </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
@@ -6174,9 +7598,18 @@
       <c r="E202">
         <v>1</v>
       </c>
-      <c r="G202" s="3"/>
-      <c r="H202" s="3"/>
-      <c r="I202" s="3"/>
+      <c r="F202" s="3">
+        <v>102689482970.10001</v>
+      </c>
+      <c r="G202">
+        <v>4.9709179999999993</v>
+      </c>
+      <c r="H202">
+        <v>36.602391000000004</v>
+      </c>
+      <c r="I202">
+        <v>36.600591999999999</v>
+      </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
@@ -6194,9 +7627,18 @@
       <c r="E203">
         <v>1</v>
       </c>
-      <c r="G203" s="3"/>
-      <c r="H203" s="3"/>
-      <c r="I203" s="3"/>
+      <c r="F203" s="3">
+        <v>102689482970.10001</v>
+      </c>
+      <c r="G203">
+        <v>4.9746319999999997</v>
+      </c>
+      <c r="H203">
+        <v>36.628932999999996</v>
+      </c>
+      <c r="I203">
+        <v>36.627131999999996</v>
+      </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
@@ -6214,9 +7656,18 @@
       <c r="E204">
         <v>1</v>
       </c>
-      <c r="G204" s="3"/>
-      <c r="H204" s="3"/>
-      <c r="I204" s="3"/>
+      <c r="F204" s="3">
+        <v>102689482970.10001</v>
+      </c>
+      <c r="G204">
+        <v>4.9781219999999999</v>
+      </c>
+      <c r="H204">
+        <v>36.653827</v>
+      </c>
+      <c r="I204">
+        <v>36.652023999999997</v>
+      </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
@@ -6234,9 +7685,18 @@
       <c r="E205">
         <v>1</v>
       </c>
-      <c r="G205" s="3"/>
-      <c r="H205" s="3"/>
-      <c r="I205" s="3"/>
+      <c r="F205" s="3">
+        <v>101784986762.86</v>
+      </c>
+      <c r="G205">
+        <v>4.9815209999999999</v>
+      </c>
+      <c r="H205">
+        <v>36.678049000000001</v>
+      </c>
+      <c r="I205">
+        <v>36.676243999999997</v>
+      </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
@@ -6254,9 +7714,18 @@
       <c r="E206">
         <v>1</v>
       </c>
-      <c r="G206" s="3"/>
-      <c r="H206" s="3"/>
-      <c r="I206" s="3"/>
+      <c r="F206" s="3">
+        <v>104826390266.57999</v>
+      </c>
+      <c r="G206">
+        <v>4.9913289999999995</v>
+      </c>
+      <c r="H206">
+        <v>36.747843000000003</v>
+      </c>
+      <c r="I206">
+        <v>36.746035000000006</v>
+      </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
@@ -6274,9 +7743,18 @@
       <c r="E207">
         <v>1</v>
       </c>
-      <c r="G207" s="3"/>
-      <c r="H207" s="3"/>
-      <c r="I207" s="3"/>
+      <c r="F207" s="3">
+        <v>127548941969.26999</v>
+      </c>
+      <c r="G207">
+        <v>4.9946719999999996</v>
+      </c>
+      <c r="H207">
+        <v>36.771646000000004</v>
+      </c>
+      <c r="I207">
+        <v>36.769837000000003</v>
+      </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
@@ -6294,9 +7772,18 @@
       <c r="E208">
         <v>1</v>
       </c>
-      <c r="G208" s="3"/>
-      <c r="H208" s="3"/>
-      <c r="I208" s="3"/>
+      <c r="F208" s="3">
+        <v>121450483663.47</v>
+      </c>
+      <c r="G208">
+        <v>4.9985670000000004</v>
+      </c>
+      <c r="H208">
+        <v>36.799517000000002</v>
+      </c>
+      <c r="I208">
+        <v>36.797705999999998</v>
+      </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
@@ -6314,9 +7801,18 @@
       <c r="E209">
         <v>1</v>
       </c>
-      <c r="G209" s="3"/>
-      <c r="H209" s="3"/>
-      <c r="I209" s="3"/>
+      <c r="F209" s="3">
+        <v>122286813136.19</v>
+      </c>
+      <c r="G209">
+        <v>5.0022879999999992</v>
+      </c>
+      <c r="H209">
+        <v>36.826105000000005</v>
+      </c>
+      <c r="I209">
+        <v>36.824292</v>
+      </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
@@ -6334,9 +7830,18 @@
       <c r="E210">
         <v>1</v>
       </c>
-      <c r="G210" s="3"/>
-      <c r="H210" s="3"/>
-      <c r="I210" s="3"/>
+      <c r="F210" s="3">
+        <v>122286813136.19</v>
+      </c>
+      <c r="G210">
+        <v>5.0059129999999996</v>
+      </c>
+      <c r="H210">
+        <v>36.851983999999995</v>
+      </c>
+      <c r="I210">
+        <v>36.850169999999999</v>
+      </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
@@ -6354,9 +7859,18 @@
       <c r="E211">
         <v>1</v>
       </c>
-      <c r="G211" s="3"/>
-      <c r="H211" s="3"/>
-      <c r="I211" s="3"/>
+      <c r="F211" s="3">
+        <v>122286813136.19</v>
+      </c>
+      <c r="G211">
+        <v>5.0172110000000005</v>
+      </c>
+      <c r="H211">
+        <v>36.932721999999998</v>
+      </c>
+      <c r="I211">
+        <v>36.930904999999996</v>
+      </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
@@ -6374,9 +7888,18 @@
       <c r="E212">
         <v>1</v>
       </c>
-      <c r="G212" s="3"/>
-      <c r="H212" s="3"/>
-      <c r="I212" s="3"/>
+      <c r="F212" s="3">
+        <v>115430740207.25</v>
+      </c>
+      <c r="G212">
+        <v>5.0208940000000002</v>
+      </c>
+      <c r="H212">
+        <v>36.959021999999997</v>
+      </c>
+      <c r="I212">
+        <v>36.957203999999997</v>
+      </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
@@ -6394,9 +7917,18 @@
       <c r="E213">
         <v>1</v>
       </c>
-      <c r="G213" s="3"/>
-      <c r="H213" s="3"/>
-      <c r="I213" s="3"/>
+      <c r="F213" s="3">
+        <v>144105242375.51999</v>
+      </c>
+      <c r="G213">
+        <v>5.0246740000000001</v>
+      </c>
+      <c r="H213">
+        <v>36.986035999999999</v>
+      </c>
+      <c r="I213">
+        <v>36.984216999999994</v>
+      </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
@@ -6414,9 +7946,18 @@
       <c r="E214">
         <v>1</v>
       </c>
-      <c r="G214" s="3"/>
-      <c r="H214" s="3"/>
-      <c r="I214" s="3"/>
+      <c r="F214" s="3">
+        <v>160030621854.51001</v>
+      </c>
+      <c r="G214">
+        <v>5.0284250000000004</v>
+      </c>
+      <c r="H214">
+        <v>37.012836999999998</v>
+      </c>
+      <c r="I214">
+        <v>37.011016000000005</v>
+      </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
@@ -6434,9 +7975,18 @@
       <c r="E215">
         <v>1</v>
       </c>
-      <c r="G215" s="3"/>
-      <c r="H215" s="3"/>
-      <c r="I215" s="3"/>
+      <c r="F215" s="3">
+        <v>161082591451.00998</v>
+      </c>
+      <c r="G215">
+        <v>5.0321259999999999</v>
+      </c>
+      <c r="H215">
+        <v>37.039265</v>
+      </c>
+      <c r="I215">
+        <v>37.037442000000006</v>
+      </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
@@ -6454,9 +8004,18 @@
       <c r="E216">
         <v>1</v>
       </c>
-      <c r="G216" s="3"/>
-      <c r="H216" s="3"/>
-      <c r="I216" s="3"/>
+      <c r="F216" s="3">
+        <v>146308187660.19</v>
+      </c>
+      <c r="G216">
+        <v>5.0415600000000005</v>
+      </c>
+      <c r="H216">
+        <v>37.106259000000001</v>
+      </c>
+      <c r="I216">
+        <v>37.104430999999998</v>
+      </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
@@ -6474,9 +8033,18 @@
       <c r="E217">
         <v>1</v>
       </c>
-      <c r="G217" s="3"/>
-      <c r="H217" s="3"/>
-      <c r="I217" s="3"/>
+      <c r="F217" s="3">
+        <v>146308187660.19</v>
+      </c>
+      <c r="G217">
+        <v>5.044708</v>
+      </c>
+      <c r="H217">
+        <v>37.128612000000004</v>
+      </c>
+      <c r="I217">
+        <v>37.126781999999999</v>
+      </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
@@ -6494,9 +8062,18 @@
       <c r="E218">
         <v>1</v>
       </c>
-      <c r="G218" s="3"/>
-      <c r="H218" s="3"/>
-      <c r="I218" s="3"/>
+      <c r="F218" s="3">
+        <v>146308187660.19</v>
+      </c>
+      <c r="G218">
+        <v>5.0474350000000001</v>
+      </c>
+      <c r="H218">
+        <v>37.147863999999998</v>
+      </c>
+      <c r="I218">
+        <v>37.146031999999998</v>
+      </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
@@ -6514,9 +8091,18 @@
       <c r="E219">
         <v>1</v>
       </c>
-      <c r="G219" s="3"/>
-      <c r="H219" s="3"/>
-      <c r="I219" s="3"/>
+      <c r="F219" s="3">
+        <v>139386432439.15002</v>
+      </c>
+      <c r="G219">
+        <v>5.0500810000000005</v>
+      </c>
+      <c r="H219">
+        <v>37.166522000000001</v>
+      </c>
+      <c r="I219">
+        <v>37.164688000000005</v>
+      </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
@@ -6534,9 +8120,18 @@
       <c r="E220">
         <v>1</v>
       </c>
-      <c r="G220" s="3"/>
-      <c r="H220" s="3"/>
-      <c r="I220" s="3"/>
+      <c r="F220" s="3">
+        <v>120597171503.20999</v>
+      </c>
+      <c r="G220">
+        <v>5.0529889999999993</v>
+      </c>
+      <c r="H220">
+        <v>37.187108000000002</v>
+      </c>
+      <c r="I220">
+        <v>37.185273000000002</v>
+      </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
@@ -6554,9 +8149,18 @@
       <c r="E221">
         <v>1</v>
       </c>
-      <c r="G221" s="3"/>
-      <c r="H221" s="3"/>
-      <c r="I221" s="3"/>
+      <c r="F221" s="3">
+        <v>119704050601.99998</v>
+      </c>
+      <c r="G221">
+        <v>5.0631490000000001</v>
+      </c>
+      <c r="H221">
+        <v>37.259430999999999</v>
+      </c>
+      <c r="I221">
+        <v>37.257591999999995</v>
+      </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
@@ -6574,9 +8178,18 @@
       <c r="E222">
         <v>1</v>
       </c>
-      <c r="G222" s="3"/>
-      <c r="H222" s="3"/>
-      <c r="I222" s="3"/>
+      <c r="F222" s="3">
+        <v>104888985602.26001</v>
+      </c>
+      <c r="G222">
+        <v>5.0669789999999999</v>
+      </c>
+      <c r="H222">
+        <v>37.286799999999999</v>
+      </c>
+      <c r="I222">
+        <v>37.284959999999998</v>
+      </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
@@ -6594,9 +8207,18 @@
       <c r="E223">
         <v>1</v>
       </c>
-      <c r="G223" s="3"/>
-      <c r="H223" s="3"/>
-      <c r="I223" s="3"/>
+      <c r="F223" s="3">
+        <v>104888985602.26001</v>
+      </c>
+      <c r="G223">
+        <v>5.0705819999999999</v>
+      </c>
+      <c r="H223">
+        <v>37.312497</v>
+      </c>
+      <c r="I223">
+        <v>37.310656000000002</v>
+      </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
@@ -6614,9 +8236,18 @@
       <c r="E224">
         <v>1</v>
       </c>
-      <c r="G224" s="3"/>
-      <c r="H224" s="3"/>
-      <c r="I224" s="3"/>
+      <c r="F224" s="3">
+        <v>104888985602.26001</v>
+      </c>
+      <c r="G224">
+        <v>5.0740460000000001</v>
+      </c>
+      <c r="H224">
+        <v>37.337164999999999</v>
+      </c>
+      <c r="I224">
+        <v>37.335322999999995</v>
+      </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
@@ -6634,9 +8265,18 @@
       <c r="E225">
         <v>1</v>
       </c>
-      <c r="G225" s="3"/>
-      <c r="H225" s="3"/>
-      <c r="I225" s="3"/>
+      <c r="F225" s="3">
+        <v>104888985602.26001</v>
+      </c>
+      <c r="G225">
+        <v>5.077318</v>
+      </c>
+      <c r="H225">
+        <v>37.360425000000006</v>
+      </c>
+      <c r="I225">
+        <v>37.358582000000006</v>
+      </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
@@ -6654,9 +8294,18 @@
       <c r="E226">
         <v>1</v>
       </c>
-      <c r="G226" s="3"/>
-      <c r="H226" s="3"/>
-      <c r="I226" s="3"/>
+      <c r="F226" s="3">
+        <v>87065144357.830002</v>
+      </c>
+      <c r="G226">
+        <v>5.0874920000000001</v>
+      </c>
+      <c r="H226">
+        <v>37.432824000000004</v>
+      </c>
+      <c r="I226">
+        <v>37.430978000000003</v>
+      </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
@@ -6674,9 +8323,18 @@
       <c r="E227">
         <v>1</v>
       </c>
-      <c r="G227" s="3"/>
-      <c r="H227" s="3"/>
-      <c r="I227" s="3"/>
+      <c r="F227" s="3">
+        <v>69496786280.589996</v>
+      </c>
+      <c r="G227">
+        <v>5.0907929999999997</v>
+      </c>
+      <c r="H227">
+        <v>37.456294</v>
+      </c>
+      <c r="I227">
+        <v>37.454447000000002</v>
+      </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
@@ -6694,9 +8352,18 @@
       <c r="E228">
         <v>1</v>
       </c>
-      <c r="G228" s="3"/>
-      <c r="H228" s="3"/>
-      <c r="I228" s="3"/>
+      <c r="F228" s="3">
+        <v>74725449701.900009</v>
+      </c>
+      <c r="G228">
+        <v>5.0940479999999999</v>
+      </c>
+      <c r="H228">
+        <v>37.479421000000002</v>
+      </c>
+      <c r="I228">
+        <v>37.477573</v>
+      </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
@@ -6714,9 +8381,18 @@
       <c r="E229">
         <v>1</v>
       </c>
-      <c r="G229" s="3"/>
-      <c r="H229" s="3"/>
-      <c r="I229" s="3"/>
+      <c r="F229" s="3">
+        <v>65063423744.849998</v>
+      </c>
+      <c r="G229">
+        <v>5.097213</v>
+      </c>
+      <c r="H229">
+        <v>37.501887000000004</v>
+      </c>
+      <c r="I229">
+        <v>37.500038000000004</v>
+      </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
@@ -6734,9 +8410,18 @@
       <c r="E230">
         <v>1</v>
       </c>
-      <c r="G230" s="3"/>
-      <c r="H230" s="3"/>
-      <c r="I230" s="3"/>
+      <c r="F230" s="3">
+        <v>78320293577.5</v>
+      </c>
+      <c r="G230">
+        <v>5.1008620000000002</v>
+      </c>
+      <c r="H230">
+        <v>37.527906999999999</v>
+      </c>
+      <c r="I230">
+        <v>37.526057000000002</v>
+      </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
@@ -6754,9 +8439,18 @@
       <c r="E231">
         <v>1</v>
       </c>
-      <c r="G231" s="3"/>
-      <c r="H231" s="3"/>
-      <c r="I231" s="3"/>
+      <c r="F231" s="3">
+        <v>78320293577.5</v>
+      </c>
+      <c r="G231">
+        <v>5.1209930000000004</v>
+      </c>
+      <c r="H231">
+        <v>37.671875999999997</v>
+      </c>
+      <c r="I231">
+        <v>37.670021999999996</v>
+      </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
@@ -6774,9 +8468,18 @@
       <c r="E232">
         <v>1</v>
       </c>
-      <c r="G232" s="3"/>
-      <c r="H232" s="3"/>
-      <c r="I232" s="3"/>
+      <c r="F232" s="3">
+        <v>78320293577.5</v>
+      </c>
+      <c r="G232">
+        <v>5.1250739999999997</v>
+      </c>
+      <c r="H232">
+        <v>37.701072000000003</v>
+      </c>
+      <c r="I232">
+        <v>37.699216</v>
+      </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
@@ -6794,9 +8497,18 @@
       <c r="E233">
         <v>1</v>
       </c>
-      <c r="G233" s="3"/>
-      <c r="H233" s="3"/>
-      <c r="I233" s="3"/>
+      <c r="F233" s="3">
+        <v>79237189305.009995</v>
+      </c>
+      <c r="G233">
+        <v>5.1294799999999992</v>
+      </c>
+      <c r="H233">
+        <v>37.732652000000002</v>
+      </c>
+      <c r="I233">
+        <v>37.730792999999998</v>
+      </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
@@ -6814,9 +8526,18 @@
       <c r="E234">
         <v>1</v>
       </c>
-      <c r="G234" s="3"/>
-      <c r="H234" s="3"/>
-      <c r="I234" s="3"/>
+      <c r="F234" s="3">
+        <v>84648865063.770004</v>
+      </c>
+      <c r="G234">
+        <v>5.1420839999999997</v>
+      </c>
+      <c r="H234">
+        <v>37.822876999999998</v>
+      </c>
+      <c r="I234">
+        <v>37.821007999999999</v>
+      </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
@@ -6834,9 +8555,18 @@
       <c r="E235">
         <v>1</v>
       </c>
-      <c r="G235" s="3"/>
-      <c r="H235" s="3"/>
-      <c r="I235" s="3"/>
+      <c r="F235" s="3">
+        <v>88849708274.280014</v>
+      </c>
+      <c r="G235">
+        <v>5.1460799999999995</v>
+      </c>
+      <c r="H235">
+        <v>37.851436</v>
+      </c>
+      <c r="I235">
+        <v>37.849565000000005</v>
+      </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
@@ -6854,9 +8584,18 @@
       <c r="E236">
         <v>1</v>
       </c>
-      <c r="G236" s="3"/>
-      <c r="H236" s="3"/>
-      <c r="I236" s="3"/>
+      <c r="F236" s="3">
+        <v>74682007236.25</v>
+      </c>
+      <c r="G236">
+        <v>5.1497259999999994</v>
+      </c>
+      <c r="H236">
+        <v>37.877419000000003</v>
+      </c>
+      <c r="I236">
+        <v>37.875546</v>
+      </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
@@ -6874,9 +8613,18 @@
       <c r="E237">
         <v>1</v>
       </c>
-      <c r="G237" s="3"/>
-      <c r="H237" s="3"/>
-      <c r="I237" s="3"/>
+      <c r="F237" s="3">
+        <v>62232242292.379997</v>
+      </c>
+      <c r="G237">
+        <v>5.1526670000000001</v>
+      </c>
+      <c r="H237">
+        <v>37.898214999999993</v>
+      </c>
+      <c r="I237">
+        <v>37.896338999999998</v>
+      </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
@@ -6894,9 +8642,18 @@
       <c r="E238">
         <v>1</v>
       </c>
-      <c r="G238" s="3"/>
-      <c r="H238" s="3"/>
-      <c r="I238" s="3"/>
+      <c r="F238" s="3">
+        <v>62232242292.379997</v>
+      </c>
+      <c r="G238">
+        <v>5.1554009999999995</v>
+      </c>
+      <c r="H238">
+        <v>37.917490000000001</v>
+      </c>
+      <c r="I238">
+        <v>37.915610999999998</v>
+      </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
@@ -6914,9 +8671,18 @@
       <c r="E239">
         <v>1</v>
       </c>
-      <c r="G239" s="3"/>
-      <c r="H239" s="3"/>
-      <c r="I239" s="3"/>
+      <c r="F239" s="3">
+        <v>62232242292.379997</v>
+      </c>
+      <c r="G239">
+        <v>5.1638019999999996</v>
+      </c>
+      <c r="H239">
+        <v>37.976779000000001</v>
+      </c>
+      <c r="I239">
+        <v>37.974896999999999</v>
+      </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
@@ -6934,9 +8700,18 @@
       <c r="E240">
         <v>1</v>
       </c>
-      <c r="G240" s="3"/>
-      <c r="H240" s="3"/>
-      <c r="I240" s="3"/>
+      <c r="F240" s="3">
+        <v>83642722606.519989</v>
+      </c>
+      <c r="G240">
+        <v>5.166696</v>
+      </c>
+      <c r="H240">
+        <v>37.997228999999997</v>
+      </c>
+      <c r="I240">
+        <v>37.995345999999998</v>
+      </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
@@ -6954,9 +8729,18 @@
       <c r="E241">
         <v>1</v>
       </c>
-      <c r="G241" s="3"/>
-      <c r="H241" s="3"/>
-      <c r="I241" s="3"/>
+      <c r="F241" s="3">
+        <v>64297447550.649994</v>
+      </c>
+      <c r="G241">
+        <v>5.1696429999999998</v>
+      </c>
+      <c r="H241">
+        <v>38.018067000000002</v>
+      </c>
+      <c r="I241">
+        <v>38.016182000000001</v>
+      </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
@@ -6974,9 +8758,18 @@
       <c r="E242">
         <v>1</v>
       </c>
-      <c r="G242" s="3"/>
-      <c r="H242" s="3"/>
-      <c r="I242" s="3"/>
+      <c r="F242" s="3">
+        <v>83250490498.600006</v>
+      </c>
+      <c r="G242">
+        <v>5.1725580000000004</v>
+      </c>
+      <c r="H242">
+        <v>38.038668999999999</v>
+      </c>
+      <c r="I242">
+        <v>38.036783</v>
+      </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
@@ -6994,9 +8787,18 @@
       <c r="E243">
         <v>1</v>
       </c>
-      <c r="G243" s="3"/>
-      <c r="H243" s="3"/>
-      <c r="I243" s="3"/>
+      <c r="F243" s="3">
+        <v>82930038429.559998</v>
+      </c>
+      <c r="G243">
+        <v>5.175529</v>
+      </c>
+      <c r="H243">
+        <v>38.059685999999999</v>
+      </c>
+      <c r="I243">
+        <v>38.057798000000005</v>
+      </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
@@ -7014,9 +8816,18 @@
       <c r="E244">
         <v>1</v>
       </c>
-      <c r="G244" s="3"/>
-      <c r="H244" s="3"/>
-      <c r="I244" s="3"/>
+      <c r="F244" s="3">
+        <v>79588089434.979996</v>
+      </c>
+      <c r="G244">
+        <v>5.1847340000000006</v>
+      </c>
+      <c r="H244">
+        <v>38.124868999999997</v>
+      </c>
+      <c r="I244">
+        <v>38.122976999999999</v>
+      </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
@@ -7034,9 +8845,18 @@
       <c r="E245">
         <v>1</v>
       </c>
-      <c r="G245" s="3"/>
-      <c r="H245" s="3"/>
-      <c r="I245" s="3"/>
+      <c r="F245" s="3">
+        <v>79588089434.979996</v>
+      </c>
+      <c r="G245">
+        <v>5.1876199999999999</v>
+      </c>
+      <c r="H245">
+        <v>38.145257000000001</v>
+      </c>
+      <c r="I245">
+        <v>38.143363000000001</v>
+      </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
@@ -7054,9 +8874,18 @@
       <c r="E246">
         <v>1</v>
       </c>
-      <c r="G246" s="3"/>
-      <c r="H246" s="3"/>
-      <c r="I246" s="3"/>
+      <c r="F246" s="3">
+        <v>79588089434.979996</v>
+      </c>
+      <c r="G246">
+        <v>5.190588</v>
+      </c>
+      <c r="H246">
+        <v>38.166241999999997</v>
+      </c>
+      <c r="I246">
+        <v>38.164345000000004</v>
+      </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
@@ -7074,9 +8903,18 @@
       <c r="E247">
         <v>1</v>
       </c>
-      <c r="G247" s="3"/>
-      <c r="H247" s="3"/>
-      <c r="I247" s="3"/>
+      <c r="F247" s="3">
+        <v>83953068845.149994</v>
+      </c>
+      <c r="G247">
+        <v>5.1934359999999993</v>
+      </c>
+      <c r="H247">
+        <v>38.186345000000003</v>
+      </c>
+      <c r="I247">
+        <v>38.184444000000006</v>
+      </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
@@ -7094,9 +8932,18 @@
       <c r="E248">
         <v>1</v>
       </c>
-      <c r="G248" s="3"/>
-      <c r="H248" s="3"/>
-      <c r="I248" s="3"/>
+      <c r="F248" s="3">
+        <v>90516750349.850006</v>
+      </c>
+      <c r="G248">
+        <v>5.1962820000000001</v>
+      </c>
+      <c r="H248">
+        <v>38.206434999999999</v>
+      </c>
+      <c r="I248">
+        <v>38.204529999999998</v>
+      </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
@@ -7114,9 +8961,18 @@
       <c r="E249">
         <v>1</v>
       </c>
-      <c r="G249" s="3"/>
-      <c r="H249" s="3"/>
-      <c r="I249" s="3"/>
+      <c r="F249" s="3">
+        <v>109667441687.92999</v>
+      </c>
+      <c r="G249">
+        <v>5.2050140000000003</v>
+      </c>
+      <c r="H249">
+        <v>38.268120000000003</v>
+      </c>
+      <c r="I249">
+        <v>38.266205999999997</v>
+      </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
@@ -7134,9 +8990,18 @@
       <c r="E250">
         <v>1</v>
       </c>
-      <c r="G250" s="3"/>
-      <c r="H250" s="3"/>
-      <c r="I250" s="3"/>
+      <c r="F250" s="3">
+        <v>109667441687.92999</v>
+      </c>
+      <c r="G250">
+        <v>5.2078930000000003</v>
+      </c>
+      <c r="H250">
+        <v>38.288446</v>
+      </c>
+      <c r="I250">
+        <v>38.286529000000002</v>
+      </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
@@ -7154,9 +9019,18 @@
       <c r="E251">
         <v>1</v>
       </c>
-      <c r="G251" s="3"/>
-      <c r="H251" s="3"/>
-      <c r="I251" s="3"/>
+      <c r="F251" s="3">
+        <v>99509947232.639999</v>
+      </c>
+      <c r="G251">
+        <v>5.2106170000000001</v>
+      </c>
+      <c r="H251">
+        <v>38.307627999999994</v>
+      </c>
+      <c r="I251">
+        <v>38.305712</v>
+      </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
@@ -7174,9 +9048,18 @@
       <c r="E252">
         <v>1</v>
       </c>
-      <c r="G252" s="3"/>
-      <c r="H252" s="3"/>
-      <c r="I252" s="3"/>
+      <c r="F252" s="3">
+        <v>99509947232.639999</v>
+      </c>
+      <c r="G252">
+        <v>5.213228</v>
+      </c>
+      <c r="H252">
+        <v>38.325983000000001</v>
+      </c>
+      <c r="I252">
+        <v>38.324067999999997</v>
+      </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
@@ -7194,9 +9077,18 @@
       <c r="E253">
         <v>1</v>
       </c>
-      <c r="G253" s="3"/>
-      <c r="H253" s="3"/>
-      <c r="I253" s="3"/>
+      <c r="F253" s="3">
+        <v>99509947232.639999</v>
+      </c>
+      <c r="G253">
+        <v>5.2159230000000001</v>
+      </c>
+      <c r="H253">
+        <v>38.344954999999999</v>
+      </c>
+      <c r="I253">
+        <v>38.343040000000002</v>
+      </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
@@ -7214,9 +9106,18 @@
       <c r="E254">
         <v>1</v>
       </c>
-      <c r="G254" s="3"/>
-      <c r="H254" s="3"/>
-      <c r="I254" s="3"/>
+      <c r="F254" s="3">
+        <v>96631401130.76001</v>
+      </c>
+      <c r="G254">
+        <v>5.229393</v>
+      </c>
+      <c r="H254">
+        <v>38.43976</v>
+      </c>
+      <c r="I254">
+        <v>38.437847000000005</v>
+      </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
@@ -7234,9 +9135,18 @@
       <c r="E255">
         <v>1</v>
       </c>
-      <c r="G255" s="3"/>
-      <c r="H255" s="3"/>
-      <c r="I255" s="3"/>
+      <c r="F255" s="3">
+        <v>100558765962.58</v>
+      </c>
+      <c r="G255">
+        <v>5.2321490000000006</v>
+      </c>
+      <c r="H255">
+        <v>38.459178000000001</v>
+      </c>
+      <c r="I255">
+        <v>38.457265</v>
+      </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
@@ -7254,9 +9164,18 @@
       <c r="E256">
         <v>1</v>
       </c>
-      <c r="G256" s="3"/>
-      <c r="H256" s="3"/>
-      <c r="I256" s="3"/>
+      <c r="F256" s="3">
+        <v>99439834897.25</v>
+      </c>
+      <c r="G256">
+        <v>5.2350320000000004</v>
+      </c>
+      <c r="H256">
+        <v>38.479520999999998</v>
+      </c>
+      <c r="I256">
+        <v>38.477607000000006</v>
+      </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
@@ -7274,9 +9193,18 @@
       <c r="E257">
         <v>1</v>
       </c>
-      <c r="G257" s="3"/>
-      <c r="H257" s="3"/>
-      <c r="I257" s="3"/>
+      <c r="F257" s="3">
+        <v>100248982625.60001</v>
+      </c>
+      <c r="G257">
+        <v>5.2432759999999998</v>
+      </c>
+      <c r="H257">
+        <v>38.537576000000001</v>
+      </c>
+      <c r="I257">
+        <v>38.535657</v>
+      </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
@@ -7294,9 +9222,18 @@
       <c r="E258">
         <v>1</v>
       </c>
-      <c r="G258" s="3"/>
-      <c r="H258" s="3"/>
-      <c r="I258" s="3"/>
+      <c r="F258" s="3">
+        <v>92487150347.920013</v>
+      </c>
+      <c r="G258">
+        <v>5.2460320000000005</v>
+      </c>
+      <c r="H258">
+        <v>38.556986999999999</v>
+      </c>
+      <c r="I258">
+        <v>38.555065999999997</v>
+      </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
@@ -7314,9 +9251,18 @@
       <c r="E259">
         <v>1</v>
       </c>
-      <c r="G259" s="3"/>
-      <c r="H259" s="3"/>
-      <c r="I259" s="3"/>
+      <c r="F259" s="3">
+        <v>92487150347.920013</v>
+      </c>
+      <c r="G259">
+        <v>5.2488999999999999</v>
+      </c>
+      <c r="H259">
+        <v>38.577224000000001</v>
+      </c>
+      <c r="I259">
+        <v>38.575302000000001</v>
+      </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
@@ -7334,9 +9280,18 @@
       <c r="E260">
         <v>1</v>
       </c>
-      <c r="G260" s="3"/>
-      <c r="H260" s="3"/>
-      <c r="I260" s="3"/>
+      <c r="F260" s="3">
+        <v>92487150347.920013</v>
+      </c>
+      <c r="G260">
+        <v>5.2629920000000006</v>
+      </c>
+      <c r="H260">
+        <v>38.676550999999996</v>
+      </c>
+      <c r="I260">
+        <v>38.674622999999997</v>
+      </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
@@ -7354,9 +9309,18 @@
       <c r="E261">
         <v>1</v>
       </c>
-      <c r="G261" s="3"/>
-      <c r="H261" s="3"/>
-      <c r="I261" s="3"/>
+      <c r="F261" s="3">
+        <v>92057189091.740005</v>
+      </c>
+      <c r="G261">
+        <v>5.2656609999999997</v>
+      </c>
+      <c r="H261">
+        <v>38.695319000000005</v>
+      </c>
+      <c r="I261">
+        <v>38.693390000000001</v>
+      </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
@@ -7374,9 +9338,18 @@
       <c r="E262">
         <v>1</v>
       </c>
-      <c r="G262" s="3"/>
-      <c r="H262" s="3"/>
-      <c r="I262" s="3"/>
+      <c r="F262" s="3">
+        <v>107515835667.32001</v>
+      </c>
+      <c r="G262">
+        <v>5.2683360000000006</v>
+      </c>
+      <c r="H262">
+        <v>38.714124000000005</v>
+      </c>
+      <c r="I262">
+        <v>38.712194000000004</v>
+      </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
@@ -7394,9 +9367,18 @@
       <c r="E263">
         <v>1</v>
       </c>
-      <c r="G263" s="3"/>
-      <c r="H263" s="3"/>
-      <c r="I263" s="3"/>
+      <c r="F263" s="3">
+        <v>93538119197.259995</v>
+      </c>
+      <c r="G263">
+        <v>5.2710100000000004</v>
+      </c>
+      <c r="H263">
+        <v>38.732927000000004</v>
+      </c>
+      <c r="I263">
+        <v>38.730995999999998</v>
+      </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
@@ -7414,9 +9396,18 @@
       <c r="E264">
         <v>1</v>
       </c>
-      <c r="G264" s="3"/>
-      <c r="H264" s="3"/>
-      <c r="I264" s="3"/>
+      <c r="F264" s="3">
+        <v>103518978626.06</v>
+      </c>
+      <c r="G264">
+        <v>5.273803</v>
+      </c>
+      <c r="H264">
+        <v>38.752599000000004</v>
+      </c>
+      <c r="I264">
+        <v>38.750667</v>
+      </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
@@ -7434,9 +9425,18 @@
       <c r="E265">
         <v>1</v>
       </c>
-      <c r="G265" s="3"/>
-      <c r="H265" s="3"/>
-      <c r="I265" s="3"/>
+      <c r="F265" s="3">
+        <v>103518978626.06</v>
+      </c>
+      <c r="G265">
+        <v>5.2824030000000004</v>
+      </c>
+      <c r="H265">
+        <v>38.813235999999996</v>
+      </c>
+      <c r="I265">
+        <v>38.811303000000002</v>
+      </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
@@ -7454,9 +9454,18 @@
       <c r="E266">
         <v>1</v>
       </c>
-      <c r="G266" s="3"/>
-      <c r="H266" s="3"/>
-      <c r="I266" s="3"/>
+      <c r="F266" s="3">
+        <v>103518978626.06</v>
+      </c>
+      <c r="G266">
+        <v>5.2852439999999996</v>
+      </c>
+      <c r="H266">
+        <v>38.833260000000003</v>
+      </c>
+      <c r="I266">
+        <v>38.831326000000004</v>
+      </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
@@ -7474,9 +9483,18 @@
       <c r="E267">
         <v>1</v>
       </c>
-      <c r="G267" s="3"/>
-      <c r="H267" s="3"/>
-      <c r="I267" s="3"/>
+      <c r="F267" s="3">
+        <v>103518978626.06</v>
+      </c>
+      <c r="G267">
+        <v>5.2880409999999998</v>
+      </c>
+      <c r="H267">
+        <v>38.852959999999996</v>
+      </c>
+      <c r="I267">
+        <v>38.851025</v>
+      </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
@@ -7494,9 +9512,18 @@
       <c r="E268">
         <v>1</v>
       </c>
-      <c r="G268" s="3"/>
-      <c r="H268" s="3"/>
-      <c r="I268" s="3"/>
+      <c r="F268" s="3">
+        <v>103518978626.06</v>
+      </c>
+      <c r="G268">
+        <v>5.2907630000000001</v>
+      </c>
+      <c r="H268">
+        <v>38.872107999999997</v>
+      </c>
+      <c r="I268">
+        <v>38.870170999999999</v>
+      </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
@@ -7514,589 +9541,621 @@
       <c r="E269">
         <v>1</v>
       </c>
-      <c r="G269" s="3"/>
-      <c r="H269" s="3"/>
-      <c r="I269" s="3"/>
+      <c r="F269" s="3">
+        <v>111390028706.99001</v>
+      </c>
+      <c r="G269">
+        <v>5.2934809999999999</v>
+      </c>
+      <c r="H269">
+        <v>38.891224000000001</v>
+      </c>
+      <c r="I269">
+        <v>38.889285000000001</v>
+      </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G270" s="1"/>
-      <c r="H270" s="2"/>
+      <c r="F270" s="4"/>
+      <c r="G270">
+        <v>5.3017330000000005</v>
+      </c>
+      <c r="H270">
+        <v>38.949286999999998</v>
+      </c>
+      <c r="I270">
+        <v>38.94735</v>
+      </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G271" s="1"/>
-      <c r="H271" s="2"/>
+      <c r="F271" s="4"/>
+      <c r="G271">
+        <f>+B271/1000</f>
+        <v>0</v>
+      </c>
+      <c r="H271">
+        <f t="shared" ref="G259:I271" si="0">+C271/1000</f>
+        <v>0</v>
+      </c>
+      <c r="I271">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G272" s="1"/>
-      <c r="H272" s="2"/>
-    </row>
-    <row r="273" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G273" s="1"/>
-      <c r="H273" s="2"/>
-    </row>
-    <row r="274" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G274" s="1"/>
-      <c r="H274" s="2"/>
-    </row>
-    <row r="275" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G275" s="1"/>
-      <c r="H275" s="2"/>
-    </row>
-    <row r="276" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G276" s="1"/>
-      <c r="H276" s="2"/>
-    </row>
-    <row r="277" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G277" s="1"/>
-      <c r="H277" s="2"/>
-    </row>
-    <row r="278" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G278" s="1"/>
-      <c r="H278" s="2"/>
-    </row>
-    <row r="279" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G279" s="1"/>
-      <c r="H279" s="2"/>
-    </row>
-    <row r="280" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G280" s="1"/>
-      <c r="H280" s="2"/>
-    </row>
-    <row r="281" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G281" s="1"/>
-      <c r="H281" s="2"/>
-    </row>
-    <row r="282" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G282" s="1"/>
-      <c r="H282" s="2"/>
-    </row>
-    <row r="283" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G283" s="1"/>
-      <c r="H283" s="2"/>
-    </row>
-    <row r="284" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G284" s="1"/>
-      <c r="H284" s="2"/>
-    </row>
-    <row r="285" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G285" s="1"/>
-      <c r="H285" s="2"/>
-    </row>
-    <row r="286" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G286" s="1"/>
-      <c r="H286" s="2"/>
-    </row>
-    <row r="287" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G287" s="1"/>
-      <c r="H287" s="2"/>
-    </row>
-    <row r="288" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G288" s="1"/>
-      <c r="H288" s="2"/>
-    </row>
-    <row r="289" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G289" s="1"/>
-      <c r="H289" s="2"/>
-    </row>
-    <row r="290" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G290" s="1"/>
-      <c r="H290" s="2"/>
-    </row>
-    <row r="291" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G291" s="1"/>
-      <c r="H291" s="2"/>
-    </row>
-    <row r="292" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G292" s="1"/>
-      <c r="H292" s="2"/>
-    </row>
-    <row r="293" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G293" s="1"/>
-      <c r="H293" s="2"/>
-    </row>
-    <row r="294" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G294" s="1"/>
-      <c r="H294" s="2"/>
-    </row>
-    <row r="295" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G295" s="1"/>
-      <c r="H295" s="2"/>
-    </row>
-    <row r="296" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G296" s="1"/>
-      <c r="H296" s="2"/>
-    </row>
-    <row r="297" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G297" s="1"/>
-      <c r="H297" s="2"/>
-    </row>
-    <row r="298" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G298" s="1"/>
-      <c r="H298" s="2"/>
-    </row>
-    <row r="299" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G299" s="1"/>
-      <c r="H299" s="2"/>
-    </row>
-    <row r="300" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G300" s="1"/>
-      <c r="H300" s="2"/>
-    </row>
-    <row r="301" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G301" s="1"/>
-      <c r="H301" s="2"/>
-    </row>
-    <row r="302" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G302" s="1"/>
-      <c r="H302" s="2"/>
-    </row>
-    <row r="303" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G303" s="1"/>
-      <c r="H303" s="2"/>
-    </row>
-    <row r="304" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G304" s="1"/>
-      <c r="H304" s="2"/>
-    </row>
-    <row r="305" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G305" s="1"/>
-      <c r="H305" s="2"/>
-    </row>
-    <row r="306" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G306" s="1"/>
-      <c r="H306" s="2"/>
-    </row>
-    <row r="307" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G307" s="1"/>
-      <c r="H307" s="2"/>
-    </row>
-    <row r="308" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G308" s="1"/>
-      <c r="H308" s="2"/>
-    </row>
-    <row r="309" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G309" s="1"/>
-      <c r="H309" s="2"/>
-    </row>
-    <row r="310" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G310" s="1"/>
-      <c r="H310" s="2"/>
-    </row>
-    <row r="311" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G311" s="1"/>
-      <c r="H311" s="2"/>
-    </row>
-    <row r="312" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G312" s="1"/>
-      <c r="H312" s="2"/>
-    </row>
-    <row r="313" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G313" s="1"/>
-      <c r="H313" s="2"/>
-    </row>
-    <row r="314" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G314" s="1"/>
-      <c r="H314" s="2"/>
-    </row>
-    <row r="315" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G315" s="1"/>
-      <c r="H315" s="2"/>
-    </row>
-    <row r="316" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G316" s="1"/>
-      <c r="H316" s="2"/>
-    </row>
-    <row r="317" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G317" s="1"/>
-      <c r="H317" s="2"/>
-    </row>
-    <row r="318" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G318" s="1"/>
-      <c r="H318" s="2"/>
-    </row>
-    <row r="319" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G319" s="1"/>
-      <c r="H319" s="2"/>
-    </row>
-    <row r="320" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G320" s="1"/>
-      <c r="H320" s="2"/>
-    </row>
-    <row r="321" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G321" s="1"/>
-      <c r="H321" s="2"/>
-    </row>
-    <row r="322" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G322" s="1"/>
-      <c r="H322" s="2"/>
-    </row>
-    <row r="323" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G323" s="1"/>
-      <c r="H323" s="2"/>
-    </row>
-    <row r="324" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G324" s="1"/>
-      <c r="H324" s="2"/>
-    </row>
-    <row r="325" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G325" s="1"/>
-      <c r="H325" s="2"/>
-    </row>
-    <row r="326" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G326" s="1"/>
-      <c r="H326" s="2"/>
-    </row>
-    <row r="327" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G327" s="1"/>
-      <c r="H327" s="2"/>
-    </row>
-    <row r="328" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G328" s="1"/>
-      <c r="H328" s="2"/>
-    </row>
-    <row r="329" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G329" s="1"/>
-      <c r="H329" s="2"/>
-    </row>
-    <row r="330" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G330" s="1"/>
-      <c r="H330" s="2"/>
-    </row>
-    <row r="331" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G331" s="1"/>
-      <c r="H331" s="2"/>
-    </row>
-    <row r="332" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G332" s="1"/>
-      <c r="H332" s="2"/>
-    </row>
-    <row r="333" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G333" s="1"/>
-      <c r="H333" s="2"/>
-    </row>
-    <row r="334" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G334" s="1"/>
-      <c r="H334" s="2"/>
-    </row>
-    <row r="335" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G335" s="1"/>
-      <c r="H335" s="2"/>
-    </row>
-    <row r="336" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G336" s="1"/>
-      <c r="H336" s="2"/>
-    </row>
-    <row r="337" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G337" s="1"/>
-      <c r="H337" s="2"/>
-    </row>
-    <row r="338" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G338" s="1"/>
-      <c r="H338" s="2"/>
-    </row>
-    <row r="339" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G339" s="1"/>
-      <c r="H339" s="2"/>
-    </row>
-    <row r="340" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G340" s="1"/>
-      <c r="H340" s="2"/>
-    </row>
-    <row r="341" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G341" s="1"/>
-      <c r="H341" s="2"/>
-    </row>
-    <row r="342" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G342" s="1"/>
-      <c r="H342" s="2"/>
-    </row>
-    <row r="343" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G343" s="1"/>
-      <c r="H343" s="2"/>
-    </row>
-    <row r="344" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G344" s="1"/>
-      <c r="H344" s="2"/>
-    </row>
-    <row r="345" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G345" s="1"/>
-      <c r="H345" s="2"/>
-    </row>
-    <row r="346" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G346" s="1"/>
-      <c r="H346" s="2"/>
-    </row>
-    <row r="347" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G347" s="1"/>
-      <c r="H347" s="2"/>
-    </row>
-    <row r="348" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G348" s="1"/>
-      <c r="H348" s="2"/>
-    </row>
-    <row r="349" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G349" s="1"/>
-      <c r="H349" s="2"/>
-    </row>
-    <row r="350" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G350" s="1"/>
-      <c r="H350" s="2"/>
-    </row>
-    <row r="351" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G351" s="1"/>
-      <c r="H351" s="2"/>
-    </row>
-    <row r="352" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G352" s="1"/>
-      <c r="H352" s="2"/>
-    </row>
-    <row r="353" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G353" s="1"/>
-      <c r="H353" s="2"/>
-    </row>
-    <row r="354" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G354" s="1"/>
-      <c r="H354" s="2"/>
-    </row>
-    <row r="355" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G355" s="1"/>
-      <c r="H355" s="2"/>
-    </row>
-    <row r="356" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G356" s="1"/>
-      <c r="H356" s="2"/>
-    </row>
-    <row r="357" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G357" s="1"/>
-      <c r="H357" s="2"/>
-    </row>
-    <row r="358" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G358" s="1"/>
-      <c r="H358" s="2"/>
-    </row>
-    <row r="359" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G359" s="1"/>
-      <c r="H359" s="2"/>
-    </row>
-    <row r="360" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G360" s="1"/>
-      <c r="H360" s="2"/>
-    </row>
-    <row r="361" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G361" s="1"/>
-      <c r="H361" s="2"/>
-    </row>
-    <row r="362" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G362" s="1"/>
-      <c r="H362" s="2"/>
-    </row>
-    <row r="363" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G363" s="1"/>
-      <c r="H363" s="2"/>
-    </row>
-    <row r="364" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G364" s="1"/>
-      <c r="H364" s="2"/>
-    </row>
-    <row r="365" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G365" s="1"/>
-      <c r="H365" s="2"/>
-    </row>
-    <row r="366" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G366" s="1"/>
-      <c r="H366" s="2"/>
-    </row>
-    <row r="367" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G367" s="1"/>
-      <c r="H367" s="2"/>
-    </row>
-    <row r="368" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G368" s="1"/>
-      <c r="H368" s="2"/>
-    </row>
-    <row r="369" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G369" s="1"/>
-      <c r="H369" s="2"/>
-    </row>
-    <row r="370" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G370" s="1"/>
-      <c r="H370" s="2"/>
-    </row>
-    <row r="371" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G371" s="1"/>
-      <c r="H371" s="2"/>
-    </row>
-    <row r="372" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G372" s="1"/>
-      <c r="H372" s="2"/>
-    </row>
-    <row r="373" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G373" s="1"/>
-      <c r="H373" s="2"/>
-    </row>
-    <row r="374" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G374" s="1"/>
-      <c r="H374" s="2"/>
-    </row>
-    <row r="375" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G375" s="1"/>
-      <c r="H375" s="2"/>
-    </row>
-    <row r="376" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G376" s="1"/>
-      <c r="H376" s="2"/>
-    </row>
-    <row r="377" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G377" s="1"/>
-      <c r="H377" s="2"/>
-    </row>
-    <row r="378" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G378" s="1"/>
-      <c r="H378" s="2"/>
-    </row>
-    <row r="379" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G379" s="1"/>
-      <c r="H379" s="2"/>
-    </row>
-    <row r="380" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G380" s="1"/>
-      <c r="H380" s="2"/>
-    </row>
-    <row r="381" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G381" s="1"/>
-      <c r="H381" s="2"/>
-    </row>
-    <row r="382" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G382" s="1"/>
-      <c r="H382" s="2"/>
-    </row>
-    <row r="383" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G383" s="1"/>
-      <c r="H383" s="2"/>
-    </row>
-    <row r="384" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G384" s="1"/>
-      <c r="H384" s="2"/>
-    </row>
-    <row r="385" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G385" s="1"/>
-      <c r="H385" s="2"/>
-    </row>
-    <row r="386" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G386" s="1"/>
-      <c r="H386" s="2"/>
-    </row>
-    <row r="387" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G387" s="1"/>
-      <c r="H387" s="2"/>
-    </row>
-    <row r="388" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G388" s="1"/>
-      <c r="H388" s="2"/>
-    </row>
-    <row r="389" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G389" s="1"/>
-      <c r="H389" s="2"/>
-    </row>
-    <row r="390" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G390" s="1"/>
-      <c r="H390" s="2"/>
-    </row>
-    <row r="391" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G391" s="1"/>
-      <c r="H391" s="2"/>
-    </row>
-    <row r="392" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G392" s="1"/>
-      <c r="H392" s="2"/>
-    </row>
-    <row r="393" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G393" s="1"/>
-      <c r="H393" s="2"/>
-    </row>
-    <row r="394" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G394" s="1"/>
-      <c r="H394" s="2"/>
-    </row>
-    <row r="395" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G395" s="1"/>
-      <c r="H395" s="2"/>
-    </row>
-    <row r="396" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G396" s="1"/>
-      <c r="H396" s="2"/>
-    </row>
-    <row r="397" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G397" s="1"/>
-      <c r="H397" s="2"/>
-    </row>
-    <row r="398" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G398" s="1"/>
-      <c r="H398" s="2"/>
-    </row>
-    <row r="399" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G399" s="1"/>
-      <c r="H399" s="2"/>
-    </row>
-    <row r="400" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G400" s="1"/>
-      <c r="H400" s="2"/>
-    </row>
-    <row r="401" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G401" s="1"/>
-      <c r="H401" s="2"/>
-    </row>
-    <row r="402" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G402" s="1"/>
-      <c r="H402" s="2"/>
-    </row>
-    <row r="403" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G403" s="1"/>
-      <c r="H403" s="2"/>
-    </row>
-    <row r="404" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G404" s="1"/>
-      <c r="H404" s="2"/>
-    </row>
-    <row r="405" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G405" s="1"/>
-      <c r="H405" s="2"/>
-    </row>
-    <row r="406" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G406" s="1"/>
-      <c r="H406" s="2"/>
-    </row>
-    <row r="407" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G407" s="1"/>
-      <c r="H407" s="2"/>
-    </row>
-    <row r="408" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G408" s="1"/>
-      <c r="H408" s="2"/>
-    </row>
-    <row r="409" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G409" s="1"/>
-      <c r="H409" s="2"/>
-    </row>
-    <row r="410" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G410" s="1"/>
-      <c r="H410" s="2"/>
-    </row>
-    <row r="411" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G411" s="1"/>
-      <c r="H411" s="2"/>
-    </row>
-    <row r="412" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G412" s="1"/>
-      <c r="H412" s="2"/>
-    </row>
-    <row r="413" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G413" s="1"/>
-      <c r="H413" s="2"/>
-    </row>
-    <row r="414" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G414" s="1"/>
-      <c r="H414" s="2"/>
+      <c r="F272" s="4"/>
+      <c r="G272" s="4"/>
+    </row>
+    <row r="273" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F273" s="4"/>
+      <c r="G273" s="4"/>
+    </row>
+    <row r="274" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F274" s="4"/>
+      <c r="G274" s="4"/>
+    </row>
+    <row r="275" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F275" s="4"/>
+      <c r="G275" s="4"/>
+    </row>
+    <row r="276" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F276" s="4"/>
+      <c r="G276" s="4"/>
+    </row>
+    <row r="277" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F277" s="4"/>
+      <c r="G277" s="4"/>
+    </row>
+    <row r="278" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F278" s="4"/>
+      <c r="G278" s="4"/>
+    </row>
+    <row r="279" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F279" s="4"/>
+      <c r="G279" s="4"/>
+    </row>
+    <row r="280" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F280" s="4"/>
+      <c r="G280" s="4"/>
+    </row>
+    <row r="281" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F281" s="4"/>
+      <c r="G281" s="4"/>
+    </row>
+    <row r="282" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F282" s="4"/>
+      <c r="G282" s="4"/>
+    </row>
+    <row r="283" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F283" s="4"/>
+      <c r="G283" s="4"/>
+    </row>
+    <row r="284" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F284" s="4"/>
+      <c r="G284" s="4"/>
+    </row>
+    <row r="285" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F285" s="4"/>
+      <c r="G285" s="4"/>
+    </row>
+    <row r="286" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F286" s="4"/>
+      <c r="G286" s="4"/>
+    </row>
+    <row r="287" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F287" s="4"/>
+      <c r="G287" s="4"/>
+    </row>
+    <row r="288" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F288" s="4"/>
+      <c r="G288" s="4"/>
+    </row>
+    <row r="289" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F289" s="4"/>
+      <c r="G289" s="4"/>
+    </row>
+    <row r="290" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F290" s="4"/>
+      <c r="G290" s="4"/>
+    </row>
+    <row r="291" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F291" s="4"/>
+      <c r="G291" s="4"/>
+    </row>
+    <row r="292" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F292" s="4"/>
+      <c r="G292" s="4"/>
+    </row>
+    <row r="293" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F293" s="4"/>
+      <c r="G293" s="4"/>
+    </row>
+    <row r="294" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F294" s="4"/>
+      <c r="G294" s="4"/>
+    </row>
+    <row r="295" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F295" s="4"/>
+      <c r="G295" s="4"/>
+    </row>
+    <row r="296" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F296" s="4"/>
+      <c r="G296" s="4"/>
+    </row>
+    <row r="297" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F297" s="4"/>
+      <c r="G297" s="4"/>
+    </row>
+    <row r="298" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F298" s="4"/>
+      <c r="G298" s="4"/>
+    </row>
+    <row r="299" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F299" s="4"/>
+      <c r="G299" s="4"/>
+    </row>
+    <row r="300" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F300" s="4"/>
+      <c r="G300" s="4"/>
+    </row>
+    <row r="301" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F301" s="4"/>
+      <c r="G301" s="4"/>
+    </row>
+    <row r="302" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F302" s="4"/>
+      <c r="G302" s="4"/>
+    </row>
+    <row r="303" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F303" s="4"/>
+      <c r="G303" s="4"/>
+    </row>
+    <row r="304" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F304" s="4"/>
+      <c r="G304" s="4"/>
+    </row>
+    <row r="305" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F305" s="4"/>
+      <c r="G305" s="4"/>
+    </row>
+    <row r="306" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F306" s="4"/>
+      <c r="G306" s="4"/>
+    </row>
+    <row r="307" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F307" s="4"/>
+      <c r="G307" s="4"/>
+    </row>
+    <row r="308" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F308" s="4"/>
+      <c r="G308" s="4"/>
+    </row>
+    <row r="309" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F309" s="4"/>
+      <c r="G309" s="4"/>
+    </row>
+    <row r="310" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F310" s="4"/>
+      <c r="G310" s="4"/>
+    </row>
+    <row r="311" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F311" s="4"/>
+      <c r="G311" s="4"/>
+    </row>
+    <row r="312" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F312" s="4"/>
+      <c r="G312" s="4"/>
+    </row>
+    <row r="313" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F313" s="4"/>
+      <c r="G313" s="4"/>
+    </row>
+    <row r="314" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F314" s="4"/>
+      <c r="G314" s="4"/>
+    </row>
+    <row r="315" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F315" s="4"/>
+      <c r="G315" s="4"/>
+    </row>
+    <row r="316" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F316" s="4"/>
+      <c r="G316" s="4"/>
+    </row>
+    <row r="317" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F317" s="4"/>
+      <c r="G317" s="4"/>
+    </row>
+    <row r="318" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F318" s="4"/>
+      <c r="G318" s="4"/>
+    </row>
+    <row r="319" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F319" s="4"/>
+      <c r="G319" s="4"/>
+    </row>
+    <row r="320" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F320" s="4"/>
+      <c r="G320" s="4"/>
+    </row>
+    <row r="321" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F321" s="4"/>
+      <c r="G321" s="4"/>
+    </row>
+    <row r="322" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F322" s="4"/>
+      <c r="G322" s="4"/>
+    </row>
+    <row r="323" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F323" s="4"/>
+      <c r="G323" s="4"/>
+    </row>
+    <row r="324" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F324" s="4"/>
+      <c r="G324" s="4"/>
+    </row>
+    <row r="325" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F325" s="4"/>
+      <c r="G325" s="4"/>
+    </row>
+    <row r="326" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F326" s="4"/>
+      <c r="G326" s="4"/>
+    </row>
+    <row r="327" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F327" s="4"/>
+      <c r="G327" s="4"/>
+    </row>
+    <row r="328" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F328" s="4"/>
+      <c r="G328" s="4"/>
+    </row>
+    <row r="329" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F329" s="4"/>
+      <c r="G329" s="4"/>
+    </row>
+    <row r="330" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F330" s="4"/>
+      <c r="G330" s="4"/>
+    </row>
+    <row r="331" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F331" s="4"/>
+      <c r="G331" s="4"/>
+    </row>
+    <row r="332" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F332" s="4"/>
+      <c r="G332" s="4"/>
+    </row>
+    <row r="333" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F333" s="4"/>
+      <c r="G333" s="4"/>
+    </row>
+    <row r="334" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F334" s="4"/>
+      <c r="G334" s="4"/>
+    </row>
+    <row r="335" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F335" s="4"/>
+      <c r="G335" s="4"/>
+    </row>
+    <row r="336" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F336" s="4"/>
+      <c r="G336" s="4"/>
+    </row>
+    <row r="337" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F337" s="4"/>
+      <c r="G337" s="4"/>
+    </row>
+    <row r="338" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F338" s="4"/>
+      <c r="G338" s="4"/>
+    </row>
+    <row r="339" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F339" s="4"/>
+      <c r="G339" s="4"/>
+    </row>
+    <row r="340" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F340" s="4"/>
+      <c r="G340" s="4"/>
+    </row>
+    <row r="341" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F341" s="4"/>
+      <c r="G341" s="4"/>
+    </row>
+    <row r="342" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F342" s="4"/>
+      <c r="G342" s="4"/>
+    </row>
+    <row r="343" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F343" s="4"/>
+      <c r="G343" s="4"/>
+    </row>
+    <row r="344" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F344" s="4"/>
+      <c r="G344" s="4"/>
+    </row>
+    <row r="345" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F345" s="4"/>
+      <c r="G345" s="4"/>
+    </row>
+    <row r="346" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F346" s="4"/>
+      <c r="G346" s="4"/>
+    </row>
+    <row r="347" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F347" s="4"/>
+      <c r="G347" s="4"/>
+    </row>
+    <row r="348" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F348" s="4"/>
+      <c r="G348" s="4"/>
+    </row>
+    <row r="349" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F349" s="4"/>
+      <c r="G349" s="4"/>
+    </row>
+    <row r="350" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F350" s="4"/>
+      <c r="G350" s="4"/>
+    </row>
+    <row r="351" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F351" s="4"/>
+      <c r="G351" s="4"/>
+    </row>
+    <row r="352" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F352" s="4"/>
+      <c r="G352" s="4"/>
+    </row>
+    <row r="353" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F353" s="4"/>
+      <c r="G353" s="4"/>
+    </row>
+    <row r="354" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F354" s="4"/>
+      <c r="G354" s="4"/>
+    </row>
+    <row r="355" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F355" s="4"/>
+      <c r="G355" s="4"/>
+    </row>
+    <row r="356" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F356" s="4"/>
+      <c r="G356" s="4"/>
+    </row>
+    <row r="357" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F357" s="4"/>
+      <c r="G357" s="4"/>
+    </row>
+    <row r="358" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F358" s="4"/>
+      <c r="G358" s="4"/>
+    </row>
+    <row r="359" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F359" s="4"/>
+      <c r="G359" s="4"/>
+    </row>
+    <row r="360" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F360" s="4"/>
+      <c r="G360" s="4"/>
+    </row>
+    <row r="361" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F361" s="4"/>
+      <c r="G361" s="4"/>
+    </row>
+    <row r="362" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F362" s="4"/>
+      <c r="G362" s="4"/>
+    </row>
+    <row r="363" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F363" s="4"/>
+      <c r="G363" s="4"/>
+    </row>
+    <row r="364" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F364" s="4"/>
+      <c r="G364" s="4"/>
+    </row>
+    <row r="365" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F365" s="4"/>
+      <c r="G365" s="4"/>
+    </row>
+    <row r="366" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F366" s="4"/>
+      <c r="G366" s="4"/>
+    </row>
+    <row r="367" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F367" s="4"/>
+      <c r="G367" s="4"/>
+    </row>
+    <row r="368" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F368" s="4"/>
+      <c r="G368" s="4"/>
+    </row>
+    <row r="369" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F369" s="4"/>
+      <c r="G369" s="4"/>
+    </row>
+    <row r="370" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F370" s="4"/>
+      <c r="G370" s="4"/>
+    </row>
+    <row r="371" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F371" s="4"/>
+      <c r="G371" s="4"/>
+    </row>
+    <row r="372" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F372" s="4"/>
+      <c r="G372" s="4"/>
+    </row>
+    <row r="373" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F373" s="4"/>
+      <c r="G373" s="4"/>
+    </row>
+    <row r="374" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F374" s="4"/>
+      <c r="G374" s="4"/>
+    </row>
+    <row r="375" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F375" s="4"/>
+      <c r="G375" s="4"/>
+    </row>
+    <row r="376" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F376" s="4"/>
+      <c r="G376" s="4"/>
+    </row>
+    <row r="377" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F377" s="4"/>
+      <c r="G377" s="4"/>
+    </row>
+    <row r="378" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F378" s="4"/>
+      <c r="G378" s="4"/>
+    </row>
+    <row r="379" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F379" s="4"/>
+      <c r="G379" s="4"/>
+    </row>
+    <row r="380" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F380" s="4"/>
+      <c r="G380" s="4"/>
+    </row>
+    <row r="381" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F381" s="4"/>
+      <c r="G381" s="4"/>
+    </row>
+    <row r="382" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F382" s="4"/>
+      <c r="G382" s="4"/>
+    </row>
+    <row r="383" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F383" s="4"/>
+      <c r="G383" s="4"/>
+    </row>
+    <row r="384" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F384" s="4"/>
+      <c r="G384" s="4"/>
+    </row>
+    <row r="385" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F385" s="4"/>
+      <c r="G385" s="4"/>
+    </row>
+    <row r="386" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F386" s="4"/>
+      <c r="G386" s="4"/>
+    </row>
+    <row r="387" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F387" s="4"/>
+      <c r="G387" s="4"/>
+    </row>
+    <row r="388" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F388" s="4"/>
+      <c r="G388" s="4"/>
+    </row>
+    <row r="389" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F389" s="4"/>
+      <c r="G389" s="4"/>
+    </row>
+    <row r="390" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F390" s="4"/>
+      <c r="G390" s="4"/>
+    </row>
+    <row r="391" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F391" s="4"/>
+      <c r="G391" s="4"/>
+    </row>
+    <row r="392" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F392" s="4"/>
+      <c r="G392" s="4"/>
+    </row>
+    <row r="393" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F393" s="4"/>
+      <c r="G393" s="4"/>
+    </row>
+    <row r="394" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F394" s="4"/>
+      <c r="G394" s="4"/>
+    </row>
+    <row r="395" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F395" s="4"/>
+      <c r="G395" s="4"/>
+    </row>
+    <row r="396" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F396" s="4"/>
+      <c r="G396" s="4"/>
+    </row>
+    <row r="397" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F397" s="4"/>
+      <c r="G397" s="4"/>
+    </row>
+    <row r="398" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F398" s="4"/>
+      <c r="G398" s="4"/>
+    </row>
+    <row r="399" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F399" s="4"/>
+      <c r="G399" s="4"/>
+    </row>
+    <row r="400" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F400" s="4"/>
+      <c r="G400" s="4"/>
+    </row>
+    <row r="401" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F401" s="4"/>
+      <c r="G401" s="4"/>
+    </row>
+    <row r="402" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F402" s="4"/>
+      <c r="G402" s="4"/>
+    </row>
+    <row r="403" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F403" s="4"/>
+      <c r="G403" s="4"/>
+    </row>
+    <row r="404" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F404" s="4"/>
+      <c r="G404" s="4"/>
+    </row>
+    <row r="405" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F405" s="4"/>
+      <c r="G405" s="4"/>
+    </row>
+    <row r="406" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F406" s="4"/>
+      <c r="G406" s="4"/>
+    </row>
+    <row r="407" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F407" s="4"/>
+      <c r="G407" s="4"/>
+    </row>
+    <row r="408" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F408" s="4"/>
+      <c r="G408" s="4"/>
+    </row>
+    <row r="409" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F409" s="4"/>
+      <c r="G409" s="4"/>
+    </row>
+    <row r="410" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F410" s="4"/>
+      <c r="G410" s="4"/>
+    </row>
+    <row r="411" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F411" s="4"/>
+      <c r="G411" s="4"/>
+    </row>
+    <row r="412" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F412" s="4"/>
+      <c r="G412" s="4"/>
+    </row>
+    <row r="413" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F413" s="4"/>
+      <c r="G413" s="4"/>
+    </row>
+    <row r="414" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F414" s="4"/>
+      <c r="G414" s="4"/>
+    </row>
+    <row r="415" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F415" s="4"/>
+      <c r="G415" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
